--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.26</v>
+        <v>5.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>1.51</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
         <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>1.99</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
         <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.50694444445</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.51041666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.51736111111</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.53472222222</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45925.50694444445</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45925.51041666666</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45925.51736111111</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.52083333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.53472222222</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="33">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="44">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="N48" t="n">
-        <v>10</v>
+        <v>1.27</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="49">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7207,126 +7207,255 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="3" t="n">
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,14 +4797,14 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.75</v>
       </c>
-      <c r="N34" t="n">
-        <v>2</v>
-      </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,49 +5055,49 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2.25</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.02</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45925.45833333334</v>
+        <v>45925.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45925.47916666666</v>
+        <v>45925.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.47916666666</v>
       </c>
     </row>
     <row r="11">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45925.50694444445</v>
+        <v>45925.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45925.51041666666</v>
+        <v>45925.50694444445</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45925.51736111111</v>
+        <v>45925.51041666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45925.52083333334</v>
+        <v>45925.51736111111</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45925.53472222222</v>
+        <v>45925.52083333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.53472222222</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.43</v>
+        <v>2.06</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="34">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N44" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="45">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="M45" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>9.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="M48" t="n">
-        <v>6.05</v>
+        <v>2.85</v>
       </c>
       <c r="N48" t="n">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>6.05</v>
       </c>
       <c r="N49" t="n">
-        <v>9.300000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="50">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="53">
@@ -7336,126 +7336,255 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="n">
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4023,14 +4023,14 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.4</v>
       </c>
-      <c r="N28" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="M32" t="n">
         <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
         <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5316,10 +5316,10 @@
         <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,49 +5442,49 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.02</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6378,10 +6378,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>9.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -678,52 +678,52 @@
         <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="M35" t="n">
-        <v>3.19</v>
+        <v>3.51</v>
       </c>
       <c r="N35" t="n">
-        <v>2.69</v>
+        <v>1.96</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.58</v>
+        <v>1.45</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="M51" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="N51" t="n">
-        <v>9.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.33</v>
+        <v>1.8</v>
       </c>
       <c r="M53" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.8</v>
+        <v>3.33</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="N54" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -690,7 +690,7 @@
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
         <v>2.94</v>
@@ -705,7 +705,7 @@
         <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
         <v>2.05</v>
@@ -936,52 +936,52 @@
         <v>2.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Z4" t="n">
         <v>1.87</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>9.34</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>7.1</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>1.96</v>
+        <v>3.58</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.4</v>
+        <v>3.09</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.51</v>
       </c>
       <c r="N38" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.19</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.69</v>
+        <v>1.45</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.87</v>
+        <v>5.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>3.85</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6378,16 +6378,16 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M48" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N48" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6636,10 +6636,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="M51" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7506,10 +7506,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="M55" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N55" t="n">
         <v>3.2</v>
@@ -7539,16 +7539,16 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -678,13 +678,13 @@
         <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
@@ -693,7 +693,7 @@
         <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
         <v>1.33</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
         <v>3.32</v>
@@ -942,16 +942,16 @@
         <v>2.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
         <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
         <v>1.41</v>
@@ -960,7 +960,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
         <v>3.58</v>
@@ -997,7 +997,7 @@
         <v>1.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4032,34 +4032,34 @@
         <v>3.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
         <v>1.9</v>
@@ -4068,16 +4068,16 @@
         <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC29" t="n">
         <v>2.05</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.96</v>
+        <v>3.58</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5580,34 +5580,34 @@
         <v>1.45</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y40" t="n">
         <v>1.58</v>
@@ -5616,16 +5616,16 @@
         <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6612,28 +6612,28 @@
         <v>2.75</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
         <v>1.55</v>
@@ -6642,22 +6642,22 @@
         <v>2.3</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -708,10 +708,10 @@
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="n">
         <v>3.5</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
         <v>3.32</v>
@@ -966,7 +966,7 @@
         <v>3.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Z4" t="n">
         <v>1.87</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.50694444445</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.51041666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.51736111111</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45925.50694444445</v>
+        <v>45925.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45925.51041666666</v>
+        <v>45925.53472222222</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45925.51736111111</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45925.52083333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45925.53472222222</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3660,37 +3660,37 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,62 +4152,62 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.51</v>
+        <v>1.41</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.05</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.61</v>
+        <v>2.51</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>4.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="T31" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
         <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC31" t="n">
         <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O33" t="n">
         <v>2.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="T33" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="U33" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X33" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4800,16 +4800,16 @@
         <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O34" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="P34" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
         <v>3.58</v>
@@ -4824,7 +4824,7 @@
         <v>2.59</v>
       </c>
       <c r="U34" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
@@ -4836,22 +4836,22 @@
         <v>3.91</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
         <v>1.57</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O37" t="n">
         <v>3.65</v>
@@ -5202,7 +5202,7 @@
         <v>2.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
         <v>3.3</v>
@@ -5223,10 +5223,10 @@
         <v>4.45</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>2.39</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="N38" t="n">
-        <v>3.58</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="P38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH38" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.98</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5571,19 +5571,19 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.4</v>
+        <v>5.07</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="N40" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="O40" t="n">
         <v>5.54</v>
       </c>
       <c r="P40" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" t="n">
         <v>1.98</v>
@@ -5610,10 +5610,10 @@
         <v>4.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AA40" t="n">
         <v>2.41</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>2.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M47" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>9.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7386,34 +7386,34 @@
         <v>2.12</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y54" t="n">
         <v>2.35</v>
@@ -7422,16 +7422,16 @@
         <v>1.58</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="M55" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N55" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,19 +681,19 @@
         <v>3.12</v>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
         <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U2" t="n">
         <v>1.33</v>
@@ -723,7 +723,7 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>2.24</v>
       </c>
       <c r="O4" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
         <v>2.11</v>
@@ -948,22 +948,22 @@
         <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="Y4" t="n">
         <v>1.83</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2628,37 +2628,37 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>4.06</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14</v>
+        <v>2.84</v>
       </c>
       <c r="U25" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.16</v>
+        <v>3.34</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="P28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.25</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.68</v>
+        <v>3.19</v>
       </c>
       <c r="T29" t="n">
-        <v>2.84</v>
+        <v>2.59</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>3.08</v>
+        <v>3.52</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>7.1</v>
+        <v>3.98</v>
       </c>
       <c r="O30" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.1</v>
+        <v>3.85</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.51</v>
+        <v>1.98</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O31" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
         <v>3.4</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.79</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.25</v>
+        <v>2.51</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>2.46</v>
+        <v>3.42</v>
       </c>
       <c r="T33" t="n">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>2.62</v>
+        <v>4.86</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.73</v>
+        <v>2.44</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="P37" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="R37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.27</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>3.98</v>
+        <v>1.53</v>
       </c>
       <c r="O39" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.07</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>1.42</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>4.47</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.9</v>
+        <v>3.66</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="T41" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="U41" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="V41" t="n">
         <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="X41" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AC41" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="43">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>2.76</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.85</v>
+        <v>3.33</v>
       </c>
       <c r="M46" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.89583333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X47" t="n">
         <v>2.75</v>
       </c>
-      <c r="O47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y47" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.89583333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,909 +6682,6 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45925.65625</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>FC Barcelona</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M49" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
-        <v>45925.6875</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="3" t="n">
-        <v>45925.79166666666</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N51" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>8</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="3" t="n">
-        <v>45925.79166666666</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>FC Cincinnati II</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Columbus Crew II</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" s="3" t="n">
-        <v>45925.85416666666</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="3" t="n">
-        <v>45925.89583333334</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O54" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="n">
-        <v>45925.89583333334</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -684,7 +684,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="R2" t="n">
         <v>1.41</v>
@@ -708,10 +708,10 @@
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA2" t="n">
         <v>3.5</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P4" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q4" t="n">
         <v>3.05</v>
@@ -957,7 +957,7 @@
         <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
         <v>1.27</v>
@@ -969,13 +969,13 @@
         <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
         <v>1.65</v>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AH4" t="n">
         <v>1.37</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="N12" t="n">
         <v>2.83</v>
@@ -1971,22 +1971,22 @@
         <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
         <v>2.89</v>
       </c>
       <c r="T12" t="n">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -2013,7 +2013,7 @@
         <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2217,19 +2217,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
         <v>4.8</v>
@@ -2256,16 +2256,16 @@
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
         <v>1.55</v>
@@ -2287,7 +2287,7 @@
         <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2613,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2628,37 +2628,37 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2871,13 +2871,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2886,37 +2886,37 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>4.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="X23" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.96</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.24</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="T25" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="X25" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.24</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.43</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="T26" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.28</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X26" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4158,55 +4158,55 @@
         <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>3.19</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X29" t="n">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>3.21</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>3.98</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
-        <v>2.3</v>
+        <v>3.73</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.85</v>
+        <v>2.51</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.51</v>
+        <v>3.98</v>
       </c>
       <c r="O31" t="n">
-        <v>5.54</v>
+        <v>2.35</v>
       </c>
       <c r="P31" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.98</v>
+        <v>3.85</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="T31" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V31" t="n">
         <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>1.09</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>9.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>20.71</v>
       </c>
       <c r="O37" t="n">
-        <v>3.05</v>
+        <v>1.45</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>3.56</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.18</v>
+        <v>11</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.52</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>3.83</v>
+        <v>6.65</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.5</v>
+        <v>5.35</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>6.05</v>
+        <v>6.74</v>
       </c>
       <c r="N42" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>3.72</v>
       </c>
       <c r="N43" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="P43" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.92</v>
+        <v>8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S43" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="T43" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="U43" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
         <v>1.07</v>
       </c>
-      <c r="W43" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.75</v>
+        <v>3.04</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.35</v>
+        <v>2.07</v>
       </c>
       <c r="M44" t="n">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>9.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="P44" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>4.92</v>
       </c>
       <c r="R44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z44" t="n">
         <v>1.44</v>
       </c>
-      <c r="S44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA44" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.57</v>
+        <v>2.37</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.04</v>
+        <v>1.76</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
         <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O47" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="P47" t="n">
         <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="R47" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
         <v>2.59</v>
       </c>
       <c r="T47" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V47" t="n">
         <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="X47" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AA47" t="n">
         <v>3.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC47" t="n">
         <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH47" t="n">
         <v>1.85</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M48" t="n">
         <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O48" t="n">
         <v>2.9</v>
@@ -6639,22 +6639,22 @@
         <v>1.41</v>
       </c>
       <c r="X48" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA48" t="n">
         <v>4.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AD48" t="n">
         <v>1.8</v>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
         <v>1.62</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -708,10 +708,10 @@
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="n">
         <v>3.5</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
         <v>3.32</v>
@@ -969,7 +969,7 @@
         <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
         <v>3.04</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" t="n">
         <v>2.25</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1710,34 +1710,34 @@
         <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="Y10" t="n">
         <v>2.3</v>
@@ -1755,7 +1755,7 @@
         <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA21" t="n">
         <v>3.2</v>
       </c>
-      <c r="N21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,16 +3249,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
         <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
         <v>2.03</v>
@@ -3288,10 +3288,10 @@
         <v>3.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>3.34</v>
@@ -3303,7 +3303,7 @@
         <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AH22" t="n">
         <v>1.41</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>2.77</v>
+        <v>1.97</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.43</v>
+        <v>6.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.99</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.1</v>
+        <v>4.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="X24" t="n">
-        <v>3.22</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.51</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="T25" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="X26" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.66</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="O29" t="n">
-        <v>2.97</v>
+        <v>3.73</v>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.57</v>
+        <v>2.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="T29" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.82</v>
+        <v>2.31</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.21</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.99</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.51</v>
       </c>
       <c r="R30" t="n">
         <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.25</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AA30" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="O31" t="n">
         <v>2.35</v>
@@ -4449,10 +4449,10 @@
         <v>4.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
         <v>2.7</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="N32" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>5.44</v>
+        <v>2.23</v>
       </c>
       <c r="P32" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.99</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>4.52</v>
+        <v>3.58</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5058,58 +5058,58 @@
         <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O36" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S36" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="T36" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
         <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X36" t="n">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z36" t="n">
         <v>2.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AH36" t="n">
         <v>1.5</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,62 +5700,62 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5829,37 +5829,37 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M42" t="n">
-        <v>6.74</v>
+        <v>6.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q42" t="n">
         <v>1.6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="U42" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
         <v>1.11</v>
@@ -5880,7 +5880,7 @@
         <v>1.82</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD42" t="n">
         <v>2</v>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="M43" t="n">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>9.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="P43" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>4.92</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S43" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U43" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X43" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.57</v>
+        <v>2.37</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.04</v>
+        <v>1.76</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.07</v>
+        <v>1.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>3.72</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="P44" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.92</v>
+        <v>8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="T44" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V44" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="X44" t="n">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.37</v>
+        <v>2.57</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.76</v>
+        <v>3.04</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N47" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
         <v>2.63</v>
@@ -6513,10 +6513,10 @@
         <v>3.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AA47" t="n">
         <v>3.9</v>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="N48" t="n">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="O48" t="n">
         <v>2.9</v>
@@ -6636,16 +6636,16 @@
         <v>1.05</v>
       </c>
       <c r="W48" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X48" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AA48" t="n">
         <v>4.33</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.41</v>
@@ -693,10 +693,10 @@
         <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -708,13 +708,13 @@
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.22</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
         <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
         <v>3.32</v>
@@ -945,19 +945,19 @@
         <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.27</v>
@@ -969,13 +969,13 @@
         <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
         <v>1.65</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
         <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
         <v>3.35</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AC10" t="n">
         <v>1.74</v>
@@ -1771,7 +1771,7 @@
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1962,71 +1962,71 @@
         <v>2.29</v>
       </c>
       <c r="M12" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
         <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="R12" t="n">
         <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T12" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.36</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
         <v>1.57</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
         <v>4.6</v>
@@ -2229,49 +2229,49 @@
         <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
         <v>4.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
         <v>3.74</v>
       </c>
       <c r="T14" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
         <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
         <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
         <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
         <v>2.54</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
         <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
         <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3.2</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.42</v>
       </c>
-      <c r="M23" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="X23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.97</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3510,7 +3510,7 @@
         <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>3.3</v>
@@ -3519,49 +3519,49 @@
         <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3639,7 +3639,7 @@
         <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
         <v>3.3</v>
@@ -3648,49 +3648,49 @@
         <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X25" t="n">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="T26" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.26</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.66</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.57</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>2.71</v>
+        <v>2.33</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>4.47</v>
       </c>
       <c r="N30" t="n">
-        <v>1.45</v>
+        <v>6</v>
       </c>
       <c r="O30" t="n">
-        <v>5.44</v>
+        <v>2.01</v>
       </c>
       <c r="P30" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="T30" t="n">
         <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC30" t="n">
         <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>3.21</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N31" t="n">
-        <v>3.58</v>
+        <v>1.99</v>
       </c>
       <c r="O31" t="n">
-        <v>2.35</v>
+        <v>3.72</v>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>4.15</v>
+        <v>4.85</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.22</v>
+        <v>2.53</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.23</v>
+        <v>5.44</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.2</v>
+        <v>1.99</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.04</v>
+        <v>1.14</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>4.47</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.01</v>
+        <v>2.97</v>
       </c>
       <c r="P33" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="T33" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="U33" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X33" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>2.62</v>
+        <v>20</v>
       </c>
       <c r="O36" t="n">
-        <v>3.02</v>
+        <v>1.46</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>3.56</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="R36" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>3.19</v>
+        <v>4.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>4.1</v>
+        <v>6.22</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.09</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>9.01</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>20.71</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>1.45</v>
+        <v>3.02</v>
       </c>
       <c r="P37" t="n">
-        <v>3.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.18</v>
       </c>
-      <c r="S37" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.09</v>
-      </c>
       <c r="X37" t="n">
-        <v>6.65</v>
+        <v>4.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.23</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>2.74</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.35</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5832,31 +5832,31 @@
         <v>9.5</v>
       </c>
       <c r="M42" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="N42" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="O42" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="P42" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q42" t="n">
         <v>1.6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U42" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
@@ -5865,25 +5865,25 @@
         <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AA42" t="n">
         <v>2.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AD42" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5958,58 +5958,58 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="P43" t="n">
         <v>1.92</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.92</v>
+        <v>4.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
         <v>2.36</v>
       </c>
       <c r="T43" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U43" t="n">
         <v>1.24</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X43" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.8</v>
+        <v>5.49</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="AD43" t="n">
         <v>1.62</v>
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AH43" t="n">
         <v>1.76</v>
@@ -6474,31 +6474,31 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="M47" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="O47" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="P47" t="n">
         <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
         <v>2.59</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U47" t="n">
         <v>1.3</v>
@@ -6510,13 +6510,13 @@
         <v>1.35</v>
       </c>
       <c r="X47" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AA47" t="n">
         <v>3.9</v>
@@ -6528,7 +6528,7 @@
         <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
         <v>1.85</v>
@@ -6603,28 +6603,28 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="M48" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="O48" t="n">
         <v>2.9</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
         <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
         <v>3.1</v>
@@ -6633,31 +6633,31 @@
         <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="W48" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X48" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AB48" t="n">
         <v>1.16</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O6" t="n">
         <v>3.05</v>
@@ -1218,16 +1218,16 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
         <v>2.38</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2886,37 +2886,37 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M21" t="n">
         <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -3159,10 +3159,10 @@
         <v>3.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AA21" t="n">
         <v>3.34</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.1</v>
+        <v>4.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.79</v>
+        <v>3.22</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="X22" t="n">
-        <v>3.22</v>
+        <v>2.59</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>4.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X23" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,62 +3636,62 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X25" t="n">
         <v>3.22</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.59</v>
-      </c>
       <c r="Y25" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.96</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,31 +3765,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>7.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U26" t="n">
         <v>1.36</v>
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
         <v>3.22</v>
@@ -3807,7 +3807,7 @@
         <v>1.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
         <v>3.2</v>
@@ -3816,10 +3816,10 @@
         <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,58 +3894,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="P27" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>4.15</v>
+        <v>3.44</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD27" t="n">
         <v>2.15</v>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.23</v>
+        <v>5.44</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>1.99</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.04</v>
+        <v>1.14</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>3.21</v>
       </c>
       <c r="M30" t="n">
-        <v>4.47</v>
+        <v>3.67</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
-        <v>2.01</v>
+        <v>3.72</v>
       </c>
       <c r="P30" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.21</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="N31" t="n">
-        <v>1.99</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.72</v>
+        <v>2.23</v>
       </c>
       <c r="P31" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="U31" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.16</v>
       </c>
-      <c r="X31" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,58 +4668,58 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="P33" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AD33" t="n">
         <v>2.15</v>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>1.52</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="M41" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5958,55 +5958,55 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="M43" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O43" t="n">
         <v>2.62</v>
       </c>
       <c r="P43" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S43" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="T43" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U43" t="n">
         <v>1.24</v>
       </c>
       <c r="V43" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W43" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X43" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AA43" t="n">
         <v>5.49</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC43" t="n">
         <v>2.19</v>
@@ -6028,7 +6028,7 @@
         <v>1.22</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.33</v>
+        <v>1.74</v>
       </c>
       <c r="M46" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="N46" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
-        <v>4.35</v>
+        <v>2.63</v>
       </c>
       <c r="P46" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="R46" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S46" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U46" t="n">
         <v>1.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X46" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.96</v>
+        <v>3.33</v>
       </c>
       <c r="M47" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="N47" t="n">
-        <v>4.18</v>
+        <v>2.12</v>
       </c>
       <c r="O47" t="n">
-        <v>2.6</v>
+        <v>4.35</v>
       </c>
       <c r="P47" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.45</v>
+        <v>2.92</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S47" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="T47" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
         <v>1.3</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X47" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6603,19 +6603,19 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="N48" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="O48" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q48" t="n">
         <v>3.75</v>
@@ -6624,10 +6624,10 @@
         <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U48" t="n">
         <v>1.3</v>
@@ -6636,22 +6636,22 @@
         <v>1.09</v>
       </c>
       <c r="W48" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X48" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AA48" t="n">
         <v>4.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AC48" t="n">
         <v>1.92</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
         <v>2.6</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T22" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="T23" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="T24" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.97</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,31 +3636,31 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="O25" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U25" t="n">
         <v>1.36</v>
@@ -3669,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X25" t="n">
         <v>3.22</v>
@@ -3687,10 +3687,10 @@
         <v>1.26</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.1</v>
+        <v>4.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.79</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="X26" t="n">
-        <v>3.22</v>
+        <v>2.59</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>4.47</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.97</v>
+        <v>2.01</v>
       </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="T27" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="N28" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>5.44</v>
+        <v>2.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.99</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="U28" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>4.47</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>1.49</v>
       </c>
       <c r="O29" t="n">
-        <v>2.01</v>
+        <v>5.38</v>
       </c>
       <c r="P29" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.6</v>
+        <v>1.99</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="T29" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AC29" t="n">
         <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.4</v>
+        <v>1.13</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="M31" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
         <v>3.8</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.33</v>
-      </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="R33" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T33" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
         <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5187,25 +5187,25 @@
         <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
         <v>3.02</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="T37" t="n">
         <v>2.5</v>
@@ -5217,13 +5217,13 @@
         <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z37" t="n">
         <v>2.1</v>
@@ -5232,13 +5232,13 @@
         <v>2.74</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
         <v>1.5</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,62 +5313,62 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.74</v>
+        <v>3.33</v>
       </c>
       <c r="M46" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="O46" t="n">
-        <v>2.63</v>
+        <v>4.35</v>
       </c>
       <c r="P46" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="R46" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S46" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="T46" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
         <v>1.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W46" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X46" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.33</v>
+        <v>1.74</v>
       </c>
       <c r="M47" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="N47" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
-        <v>4.35</v>
+        <v>2.63</v>
       </c>
       <c r="P47" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="R47" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S47" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U47" t="n">
         <v>1.3</v>
       </c>
       <c r="V47" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X47" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,34 +669,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
         <v>3.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -705,13 +705,13 @@
         <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="n">
         <v>3.85</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
         <v>1.17</v>
@@ -822,10 +822,10 @@
         <v>4.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -834,7 +834,7 @@
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="Y3" t="n">
         <v>1.32</v>
@@ -846,13 +846,13 @@
         <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
         <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
         <v>1.59</v>
@@ -927,34 +927,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="P4" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="Q4" t="n">
         <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -969,13 +969,13 @@
         <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
         <v>1.65</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.26</v>
@@ -1218,10 +1218,10 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Y6" t="n">
         <v>1.58</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
@@ -1725,37 +1725,37 @@
         <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="M12" t="n">
         <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
         <v>1.4</v>
@@ -1995,25 +1995,25 @@
         <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
         <v>1.87</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
         <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
         <v>1.57</v>
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>4.54</v>
       </c>
       <c r="O14" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
@@ -2253,25 +2253,25 @@
         <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3129,13 +3129,13 @@
         <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P21" t="n">
         <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
         <v>1.37</v>
@@ -3153,10 +3153,10 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X21" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Y21" t="n">
         <v>1.9</v>
@@ -3168,7 +3168,7 @@
         <v>3.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
         <v>1.74</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.08</v>
+        <v>4.43</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X22" t="n">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -3411,10 +3411,10 @@
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X23" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
         <v>2.3</v>
@@ -3423,7 +3423,7 @@
         <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AB23" t="n">
         <v>1.14</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
         <v>1.61</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>6.87</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
         <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>2.54</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,62 +3636,62 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.97</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
         <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
         <v>1.6</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.66</v>
+        <v>4.47</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="T28" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>1.49</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
-        <v>5.38</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.99</v>
+        <v>3.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.48</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,16 +4410,16 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
         <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="O31" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="P31" t="n">
         <v>2.39</v>
@@ -4443,25 +4443,25 @@
         <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AB31" t="n">
         <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AD31" t="n">
         <v>2.17</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>3.01</v>
+        <v>2.23</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.72</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
         <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="O33" t="n">
-        <v>3.8</v>
+        <v>5.38</v>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.53</v>
+        <v>2.11</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
         <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O34" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.1</v>
+        <v>5.17</v>
       </c>
       <c r="R34" t="n">
         <v>1.51</v>
@@ -4821,37 +4821,37 @@
         <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V34" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X34" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5055,34 +5055,34 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>14.46</v>
       </c>
       <c r="N36" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O36" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P36" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>11.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S36" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="T36" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -5091,25 +5091,25 @@
         <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>6.22</v>
+        <v>6.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.75</v>
+        <v>5.9</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O40" t="n">
         <v>3.35</v>
       </c>
-      <c r="N40" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.8</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>1.53</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,78 +5958,78 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.79</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>3.05</v>
+        <v>6.3</v>
       </c>
       <c r="N43" t="n">
-        <v>4.3</v>
+        <v>1.23</v>
       </c>
       <c r="O43" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V43" t="n">
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.08</v>
       </c>
-      <c r="W43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.33</v>
+        <v>1.35</v>
       </c>
       <c r="M46" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="N46" t="n">
-        <v>2.12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>4.35</v>
+        <v>1.95</v>
       </c>
       <c r="P46" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.92</v>
+        <v>8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V46" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X46" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.02</v>
+        <v>2.57</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.3</v>
+        <v>3.04</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,126 +6562,513 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45925.875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="L51" t="n">
         <v>2.17</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M51" t="n">
         <v>2.87</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N51" t="n">
         <v>3.23</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T48" t="n">
+      <c r="O51" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T51" t="n">
         <v>3.2</v>
       </c>
-      <c r="U48" t="n">
+      <c r="U51" t="n">
         <v>1.3</v>
       </c>
-      <c r="V48" t="n">
+      <c r="V51" t="n">
         <v>1.09</v>
       </c>
-      <c r="W48" t="n">
+      <c r="W51" t="n">
         <v>1.5</v>
       </c>
-      <c r="X48" t="n">
+      <c r="X51" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y51" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="Z51" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA48" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
+      <c r="AA51" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -678,31 +678,31 @@
         <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>2.92</v>
@@ -714,7 +714,7 @@
         <v>1.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="AB2" t="n">
         <v>1.22</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
         <v>1.4</v>
@@ -807,10 +807,10 @@
         <v>2.7</v>
       </c>
       <c r="O3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.47</v>
       </c>
       <c r="Q3" t="n">
         <v>2.95</v>
@@ -822,7 +822,7 @@
         <v>4.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.76</v>
@@ -834,13 +834,13 @@
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="Y3" t="n">
         <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA3" t="n">
         <v>1.9</v>
@@ -852,7 +852,7 @@
         <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="n">
         <v>1.59</v>
@@ -939,31 +939,31 @@
         <v>3.39</v>
       </c>
       <c r="P4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
         <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
         <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X4" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="Y4" t="n">
         <v>1.83</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
@@ -1209,7 +1209,7 @@
         <v>3.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
         <v>1.56</v>
@@ -1218,7 +1218,7 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>4.35</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AH6" t="n">
         <v>1.44</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1710,13 +1710,13 @@
         <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.97</v>
+        <v>3.86</v>
       </c>
       <c r="P10" t="n">
         <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
@@ -1725,10 +1725,10 @@
         <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -1752,7 +1752,7 @@
         <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>2.04</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AH10" t="n">
         <v>1.31</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,31 +3120,31 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>6.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
@@ -3156,7 +3156,7 @@
         <v>1.26</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y21" t="n">
         <v>1.9</v>
@@ -3171,10 +3171,10 @@
         <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T22" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X22" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
         <v>1.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AB22" t="n">
         <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
         <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.95</v>
+        <v>4.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
         <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
         <v>1.61</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.87</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
-        <v>3.22</v>
+        <v>2.81</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.54</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3648,10 +3648,10 @@
         <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
@@ -3681,16 +3681,16 @@
         <v>1.72</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P26" t="n">
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.47</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AC28" t="n">
         <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,58 +4152,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>4.47</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.88</v>
+        <v>2.01</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="T29" t="n">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.43</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
         <v>2</v>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.58</v>
+        <v>1.45</v>
       </c>
       <c r="O31" t="n">
-        <v>2.35</v>
+        <v>4.9</v>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.06</v>
+        <v>1.09</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.62</v>
+        <v>3.09</v>
       </c>
       <c r="M32" t="n">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="N32" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="O32" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="T32" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>3.58</v>
+        <v>4.86</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
         <v>4.1</v>
       </c>
-      <c r="N33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="O33" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.13</v>
+        <v>2.01</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,77 +5055,77 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.1</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>14.46</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>1.41</v>
+        <v>3.02</v>
       </c>
       <c r="P36" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>11.9</v>
+        <v>3.22</v>
       </c>
       <c r="R36" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="T36" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="U36" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>6.95</v>
+        <v>3.75</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH36" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>1.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>14.46</v>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>17</v>
       </c>
       <c r="O37" t="n">
-        <v>3.02</v>
+        <v>1.41</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>11.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>3.04</v>
+        <v>4.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>3.82</v>
+        <v>6.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.57</v>
+        <v>2.17</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>5.8</v>
       </c>
       <c r="M40" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="O40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,62 +5700,62 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6225,34 +6225,34 @@
         <v>4.3</v>
       </c>
       <c r="O45" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="P45" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.14</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T45" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U45" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V45" t="n">
         <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X45" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="Y45" t="n">
         <v>2.35</v>
@@ -6267,10 +6267,10 @@
         <v>1.11</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.74</v>
+        <v>3.33</v>
       </c>
       <c r="M49" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="N49" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="O49" t="n">
-        <v>2.48</v>
+        <v>4.35</v>
       </c>
       <c r="P49" t="n">
         <v>1.92</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.06</v>
+        <v>2.92</v>
       </c>
       <c r="R49" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="T49" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
         <v>1.3</v>
       </c>
       <c r="V49" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W49" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X49" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.86</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.33</v>
+        <v>1.74</v>
       </c>
       <c r="M50" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O50" t="n">
-        <v>4.35</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.92</v>
+        <v>4.86</v>
       </c>
       <c r="R50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z50" t="n">
         <v>1.5</v>
       </c>
-      <c r="S50" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AA50" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6999,19 +6999,19 @@
         <v>3.23</v>
       </c>
       <c r="O51" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.85</v>
+        <v>4.06</v>
       </c>
       <c r="R51" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S51" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T51" t="n">
         <v>3.2</v>
@@ -7020,7 +7020,7 @@
         <v>1.3</v>
       </c>
       <c r="V51" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W51" t="n">
         <v>1.5</v>
@@ -7035,16 +7035,16 @@
         <v>1.48</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="M12" t="n">
         <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3.01</v>
+        <v>2.81</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U12" t="n">
         <v>1.4</v>
@@ -1992,28 +1992,28 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>4.54</v>
+        <v>4.59</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>4.92</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.74</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
@@ -2253,19 +2253,19 @@
         <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>4.42</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AA14" t="n">
         <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
         <v>1.61</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
         <v>2.3</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.1</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="T21" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.26</v>
       </c>
-      <c r="X21" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.57</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="T22" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.26</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O24" t="n">
         <v>3.2</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.75</v>
-      </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>2.84</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="O25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA25" t="n">
         <v>3.2</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.41</v>
+        <v>2.57</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>3.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="O27" t="n">
-        <v>2.23</v>
+        <v>3.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="T27" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>3.58</v>
+        <v>4.86</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="O29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH29" t="n">
         <v>2.01</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>4.47</v>
       </c>
       <c r="N31" t="n">
-        <v>1.45</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>4.9</v>
+        <v>2.01</v>
       </c>
       <c r="P31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.52</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC31" t="n">
         <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.09</v>
+        <v>5.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.51</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="T32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.25</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="N33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X33" t="n">
         <v>3.58</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.16</v>
       </c>
-      <c r="X33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH33" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.17</v>
+        <v>5.05</v>
       </c>
       <c r="R34" t="n">
         <v>1.51</v>
@@ -4821,10 +4821,10 @@
         <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V34" t="n">
         <v>1.05</v>
@@ -4836,22 +4836,22 @@
         <v>2.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC34" t="n">
         <v>2.05</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5187,31 +5187,31 @@
         <v>1.1</v>
       </c>
       <c r="M37" t="n">
-        <v>14.46</v>
+        <v>10</v>
       </c>
       <c r="N37" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O37" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="P37" t="n">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="Q37" t="n">
-        <v>11.9</v>
+        <v>13.14</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S37" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="T37" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U37" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
@@ -5220,25 +5220,25 @@
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AH37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,62 +5313,62 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.8</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>1.53</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.65</v>
+        <v>5.8</v>
       </c>
       <c r="M41" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>7.17</v>
       </c>
       <c r="P41" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="R41" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="T41" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="X41" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AA41" t="n">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5958,31 +5958,31 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9.220000000000001</v>
+        <v>10</v>
       </c>
       <c r="M43" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="N43" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="P43" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R43" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="T43" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="U43" t="n">
         <v>1.73</v>
@@ -5991,7 +5991,7 @@
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X43" t="n">
         <v>6</v>
@@ -6000,7 +6000,7 @@
         <v>1.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA43" t="n">
         <v>2.15</v>
@@ -6009,10 +6009,10 @@
         <v>1.73</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.12</v>
+        <v>3.92</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="N45" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="P45" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.33</v>
+        <v>8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V45" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W45" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X45" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.7</v>
+        <v>3.04</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="M46" t="n">
-        <v>3.72</v>
+        <v>3.05</v>
       </c>
       <c r="N46" t="n">
-        <v>9.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="P46" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S46" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T46" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U46" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W46" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X46" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.04</v>
+        <v>1.7</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1194,13 +1194,13 @@
         <v>2.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="R6" t="n">
         <v>1.26</v>
@@ -1209,16 +1209,16 @@
         <v>3.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>4.35</v>
@@ -1233,7 +1233,7 @@
         <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
         <v>1.48</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AH6" t="n">
         <v>1.44</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="M24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.25</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="25">
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
         <v>4</v>
@@ -3645,34 +3645,34 @@
         <v>7.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.1</v>
+        <v>5.89</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="T25" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="Y25" t="n">
         <v>1.9</v>
@@ -3681,16 +3681,16 @@
         <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.57</v>
+        <v>2.18</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.05</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.93</v>
-      </c>
       <c r="Q26" t="n">
-        <v>4.25</v>
+        <v>3.23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
         <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,78 +3894,78 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.09</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3.51</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>1.96</v>
+        <v>3.47</v>
       </c>
       <c r="O27" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>3.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
-        <v>4.86</v>
+        <v>2.95</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.54</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>3.64</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="X28" t="n">
-        <v>3.85</v>
+        <v>2.46</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.8</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA29" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="31">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>4.47</v>
+        <v>3.66</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="P31" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="U31" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X31" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.4</v>
+        <v>3.09</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>3.51</v>
       </c>
       <c r="N32" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="O32" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="T32" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>4.54</v>
+        <v>4.86</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y33" t="n">
         <v>1.62</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.65</v>
-      </c>
       <c r="Z33" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>2.69</v>
       </c>
       <c r="O34" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.05</v>
+        <v>3.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="T34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA34" t="n">
         <v>3.2</v>
       </c>
-      <c r="U34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="N35" t="n">
         <v>6</v>
       </c>
-      <c r="M35" t="n">
-        <v>4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.44</v>
-      </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Z35" t="n">
         <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,62 +5184,62 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="M37" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>21</v>
+        <v>1.45</v>
       </c>
       <c r="O37" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="P37" t="n">
-        <v>3.79</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>13.14</v>
+        <v>1.98</v>
       </c>
       <c r="R37" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>4.75</v>
+        <v>3.48</v>
       </c>
       <c r="T37" t="n">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="U37" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>6.9</v>
+        <v>4.54</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.76</v>
+        <v>2.52</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC37" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>6</v>
+        <v>1.09</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.65</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="O38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="N41" t="n">
-        <v>1.53</v>
+        <v>21</v>
       </c>
       <c r="O41" t="n">
-        <v>7.17</v>
+        <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>2.09</v>
+        <v>3.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.05</v>
+        <v>13.14</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="S41" t="n">
-        <v>2.52</v>
+        <v>4.75</v>
       </c>
       <c r="T41" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.61</v>
+        <v>3.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45925.66666666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>10</v>
+        <v>1.82</v>
       </c>
       <c r="M43" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.66</v>
+        <v>6.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.29</v>
+        <v>3.82</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>1.46</v>
       </c>
       <c r="O44" t="n">
-        <v>2.25</v>
+        <v>6.47</v>
       </c>
       <c r="P44" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.72</v>
+        <v>2.16</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T44" t="n">
         <v>3.1</v>
       </c>
-      <c r="T44" t="n">
-        <v>2.41</v>
-      </c>
       <c r="U44" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="X44" t="n">
-        <v>3.96</v>
+        <v>2.76</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.49</v>
+        <v>4.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.95</v>
+        <v>1.08</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.77083333334</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="M45" t="n">
-        <v>3.72</v>
+        <v>2.91</v>
       </c>
       <c r="N45" t="n">
-        <v>9.300000000000001</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>1.95</v>
+        <v>3.98</v>
       </c>
       <c r="P45" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>3.26</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S45" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="T45" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="U45" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V45" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1.4</v>
       </c>
-      <c r="X45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA45" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.04</v>
+        <v>1.32</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,77 +6345,77 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.79</v>
+        <v>3.09</v>
       </c>
       <c r="M46" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="O46" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="P46" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="R46" t="n">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="S46" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="T46" t="n">
-        <v>3.5</v>
+        <v>2.19</v>
       </c>
       <c r="U46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X46" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
         <v>1.22</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>9.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="N47" t="n">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="48">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,77 +6603,77 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M48" t="n">
-        <v>3.78</v>
+        <v>3.29</v>
       </c>
       <c r="N48" t="n">
         <v>4.7</v>
       </c>
       <c r="O48" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="P48" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.07</v>
+        <v>4.72</v>
       </c>
       <c r="R48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
         <v>1.23</v>
       </c>
-      <c r="S48" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X48" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH48" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45925.875</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.33</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="O49" t="n">
-        <v>4.35</v>
+        <v>2.65</v>
       </c>
       <c r="P49" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.92</v>
+        <v>4.33</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S49" t="n">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U49" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="X49" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="Y49" t="n">
         <v>2.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.74</v>
+        <v>1.35</v>
       </c>
       <c r="M50" t="n">
-        <v>3.23</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>4.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="P50" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.86</v>
+        <v>8</v>
       </c>
       <c r="R50" t="n">
         <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="U50" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V50" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W50" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="X50" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.99</v>
+        <v>2.57</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.85</v>
+        <v>3.04</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,126 +6949,642 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Columbus Crew II</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
+        <v>45925.85416666666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3" t="n">
+        <v>45925.875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>South America Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Chapecoense</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Avaí</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="L55" t="n">
         <v>2.17</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M55" t="n">
         <v>2.87</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N55" t="n">
         <v>3.23</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O55" t="n">
         <v>2.95</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P55" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q55" t="n">
         <v>4.06</v>
       </c>
-      <c r="R51" t="n">
+      <c r="R55" t="n">
         <v>1.46</v>
       </c>
-      <c r="S51" t="n">
+      <c r="S55" t="n">
         <v>2.62</v>
       </c>
-      <c r="T51" t="n">
+      <c r="T55" t="n">
         <v>3.2</v>
       </c>
-      <c r="U51" t="n">
+      <c r="U55" t="n">
         <v>1.3</v>
       </c>
-      <c r="V51" t="n">
+      <c r="V55" t="n">
         <v>1.05</v>
       </c>
-      <c r="W51" t="n">
+      <c r="W55" t="n">
         <v>1.5</v>
       </c>
-      <c r="X51" t="n">
+      <c r="X55" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y55" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="Z55" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AA55" t="n">
         <v>4.33</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AB55" t="n">
         <v>1.19</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AC55" t="n">
         <v>1.99</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AD55" t="n">
         <v>1.81</v>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
         <v>1.27</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AH55" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="3" t="n">
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,25 +1710,25 @@
         <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="T10" t="n">
         <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -1737,7 +1737,7 @@
         <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="Y10" t="n">
         <v>2.3</v>
@@ -1752,10 +1752,10 @@
         <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2613,52 +2613,52 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3387,52 +3387,52 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.89</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N27" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.03</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.64</v>
+        <v>7.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.14</v>
+        <v>2.18</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>5.89</v>
       </c>
       <c r="R28" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="T28" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.48</v>
+        <v>2.18</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.96</v>
+        <v>2.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
-        <v>2.47</v>
+        <v>3.48</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.74</v>
+        <v>3.23</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AC29" t="n">
         <v>1.82</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N30" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="O30" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.48</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X30" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z30" t="n">
         <v>1.55</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="M31" t="n">
-        <v>3.66</v>
+        <v>3.33</v>
       </c>
       <c r="N31" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>4.74</v>
       </c>
       <c r="R31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="X31" t="n">
-        <v>3.58</v>
+        <v>2.92</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,78 +4539,78 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.09</v>
+        <v>2.03</v>
       </c>
       <c r="M32" t="n">
-        <v>3.51</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>1.96</v>
+        <v>3.47</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>3.92</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="T32" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="X32" t="n">
-        <v>4.86</v>
+        <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.54</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="33">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="N33" t="n">
-        <v>3.58</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T33" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.41</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>4.47</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="P35" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="T35" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.1</v>
+        <v>2.63</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>4.9</v>
+        <v>3.17</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U37" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
-        <v>4.54</v>
+        <v>4.75</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Z37" t="n">
         <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>1.71</v>
       </c>
       <c r="M38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>4</v>
       </c>
-      <c r="N38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="N39" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="P39" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="T39" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA39" t="n">
         <v>3.2</v>
       </c>
-      <c r="U39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>1.34</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>4.9</v>
       </c>
       <c r="R40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U40" t="n">
         <v>1.3</v>
       </c>
-      <c r="S40" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="X40" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>21</v>
+        <v>1.44</v>
       </c>
       <c r="O41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13.14</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>13.14</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="44">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,43 +6087,43 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6.6</v>
+        <v>1.82</v>
       </c>
       <c r="M44" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>1.46</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>2.2</v>
@@ -6132,16 +6132,16 @@
         <v>1.6</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,62 +6345,62 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.09</v>
+        <v>6.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.09</v>
+        <v>3.82</v>
       </c>
       <c r="N46" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="O46" t="n">
-        <v>3.02</v>
+        <v>6.47</v>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.77</v>
+        <v>2.16</v>
       </c>
       <c r="R46" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>3.56</v>
+        <v>2.52</v>
       </c>
       <c r="T46" t="n">
-        <v>2.19</v>
+        <v>3.1</v>
       </c>
       <c r="U46" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>2.76</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.66666666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.66</v>
+        <v>3.09</v>
       </c>
       <c r="M48" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="N48" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="O48" t="n">
-        <v>2.25</v>
+        <v>3.02</v>
       </c>
       <c r="P48" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.72</v>
+        <v>2.77</v>
       </c>
       <c r="R48" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="T48" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X48" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z48" t="n">
         <v>2.41</v>
       </c>
-      <c r="U48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AA48" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC48" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AD48" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45925.77083333334</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>9.5</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="N49" t="n">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="O49" t="n">
-        <v>2.65</v>
+        <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.33</v>
+        <v>1.67</v>
       </c>
       <c r="R49" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="S49" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1.22</v>
+        <v>1.77</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="X49" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.52</v>
+        <v>2.95</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.5</v>
+        <v>2.14</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,78 +6861,78 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N50" t="n">
-        <v>9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="O50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.95</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>8</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AI50" t="n">
         <v>0</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="N51" t="n">
-        <v>3.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="M52" t="n">
-        <v>3.78</v>
+        <v>3.05</v>
       </c>
       <c r="N52" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O52" t="n">
-        <v>1.99</v>
+        <v>2.72</v>
       </c>
       <c r="P52" t="n">
-        <v>2.47</v>
+        <v>1.84</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.07</v>
+        <v>4.92</v>
       </c>
       <c r="R52" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="S52" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="T52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC52" t="n">
         <v>2.19</v>
       </c>
-      <c r="U52" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AD52" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45925.875</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.33</v>
+        <v>1.9</v>
       </c>
       <c r="M53" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="O53" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,77 +7377,77 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>3.78</v>
       </c>
       <c r="N54" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="P54" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.86</v>
+        <v>5.07</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="S54" t="n">
-        <v>2.6</v>
+        <v>3.56</v>
       </c>
       <c r="T54" t="n">
-        <v>3.22</v>
+        <v>2.19</v>
       </c>
       <c r="U54" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="V54" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W54" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="X54" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.5</v>
+        <v>2.41</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC54" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH54" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.875</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,31 +7506,31 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.17</v>
+        <v>3.33</v>
       </c>
       <c r="M55" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="N55" t="n">
-        <v>3.23</v>
+        <v>2.12</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>4.35</v>
       </c>
       <c r="P55" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.06</v>
+        <v>2.92</v>
       </c>
       <c r="R55" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="T55" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U55" t="n">
         <v>1.3</v>
@@ -7539,52 +7539,310 @@
         <v>1.05</v>
       </c>
       <c r="W55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X56" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z56" t="n">
         <v>1.5</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AA56" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X57" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Y57" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="Z57" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA55" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
+      <c r="AA57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK57"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="M2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="AB2" t="n">
         <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,13 +739,13 @@
         <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45925.22916666666</v>
@@ -807,13 +807,13 @@
         <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>1.17</v>
@@ -822,25 +822,25 @@
         <v>4.25</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AA3" t="n">
         <v>1.9</v>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
         <v>1.59</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45925.35416666666</v>
@@ -927,37 +927,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
         <v>3.39</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T4" t="n">
         <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
         <v>1.23</v>
@@ -969,19 +969,19 @@
         <v>1.83</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45925.375</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45925.43055555555</v>
+        <v>45925.42708333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45925.43402777778</v>
+        <v>45925.43055555555</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45925.4375</v>
+        <v>45925.43402777778</v>
       </c>
     </row>
     <row r="8">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>9.34</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.83</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45925.45833333334</v>
+        <v>45925.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>1.09</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>9.34</v>
       </c>
       <c r="N10" t="n">
-        <v>2.26</v>
+        <v>20</v>
       </c>
       <c r="O10" t="n">
-        <v>3.93</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>3.02</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>3.36</v>
+        <v>5.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>6.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45925.47916666666</v>
+        <v>45925.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.47916666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45925.50694444445</v>
+        <v>45925.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45925.51041666666</v>
+        <v>45925.50694444445</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45925.51736111111</v>
+        <v>45925.51041666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45925.52083333334</v>
+        <v>45925.51736111111</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45925.53472222222</v>
+        <v>45925.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,26 +2600,26 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2677,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.53125</v>
       </c>
     </row>
     <row r="18">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.53472222222</v>
       </c>
     </row>
     <row r="19">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O23" t="n">
-        <v>4.06</v>
+        <v>2.99</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.24</v>
+        <v>4.09</v>
       </c>
       <c r="R23" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>2.39</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="X23" t="n">
-        <v>4.9</v>
+        <v>2.46</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.43</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.46</v>
+        <v>2.01</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>4.4</v>
+        <v>3.47</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.04</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,43 +4023,43 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="P28" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.89</v>
+        <v>4.87</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T28" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="Y28" t="n">
         <v>1.9</v>
@@ -4068,16 +4068,16 @@
         <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.53</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.04</v>
+        <v>4.47</v>
       </c>
       <c r="N29" t="n">
-        <v>2.66</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.48</v>
+        <v>2.01</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>2.83</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.72</v>
+        <v>2.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.02</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.03</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.64</v>
+        <v>1.45</v>
       </c>
       <c r="O30" t="n">
-        <v>3.14</v>
+        <v>5.1</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>2.46</v>
+        <v>4.63</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="M31" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>3.47</v>
+        <v>2.69</v>
       </c>
       <c r="O32" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="P32" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.44</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.35</v>
       </c>
-      <c r="X32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>3.09</v>
       </c>
       <c r="M33" t="n">
-        <v>4.47</v>
+        <v>3.51</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="O33" t="n">
-        <v>2.01</v>
+        <v>3.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="U33" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="N35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U35" t="n">
         <v>1.44</v>
       </c>
-      <c r="O35" t="n">
-        <v>5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AC35" t="n">
         <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>2.63</v>
+        <v>1.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="M36" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="P36" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W36" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="X36" t="n">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.1</v>
+        <v>5.86</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="O37" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.71</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N38" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>1.1</v>
       </c>
       <c r="M39" t="n">
-        <v>2.82</v>
+        <v>9.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>16.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3.01</v>
+        <v>1.31</v>
       </c>
       <c r="P39" t="n">
-        <v>2.02</v>
+        <v>3.29</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.72</v>
+        <v>13.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>2.73</v>
+        <v>4.33</v>
       </c>
       <c r="T39" t="n">
-        <v>2.69</v>
+        <v>1.88</v>
       </c>
       <c r="U39" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.06</v>
       </c>
-      <c r="W39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X39" t="n">
-        <v>3.85</v>
+        <v>6.22</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.55</v>
+        <v>4.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.95</v>
+        <v>6.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>1.46</v>
       </c>
       <c r="O40" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="P40" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.9</v>
+        <v>2.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T40" t="n">
         <v>3.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X40" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
         <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.1</v>
+        <v>2.53</v>
       </c>
       <c r="M42" t="n">
-        <v>10</v>
+        <v>2.91</v>
       </c>
       <c r="N42" t="n">
-        <v>21</v>
+        <v>2.78</v>
       </c>
       <c r="O42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.33</v>
       </c>
-      <c r="P42" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X42" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AH42" t="n">
-        <v>6</v>
+        <v>1.38</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="M43" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.82</v>
+        <v>3.09</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.53</v>
+        <v>11</v>
       </c>
       <c r="M45" t="n">
-        <v>2.91</v>
+        <v>6.7</v>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>1.23</v>
       </c>
       <c r="O45" t="n">
-        <v>3.98</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.26</v>
+        <v>1.64</v>
       </c>
       <c r="R45" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>2.35</v>
+        <v>4.3</v>
       </c>
       <c r="T45" t="n">
-        <v>3.6</v>
+        <v>2.07</v>
       </c>
       <c r="U45" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
         <v>1.11</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X45" t="n">
-        <v>2.37</v>
+        <v>6</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.7</v>
+        <v>1.39</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AA45" t="n">
-        <v>5</v>
+        <v>2.14</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>6.6</v>
+        <v>1.66</v>
       </c>
       <c r="M46" t="n">
-        <v>3.82</v>
+        <v>3.29</v>
       </c>
       <c r="N46" t="n">
-        <v>1.46</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
-        <v>6.47</v>
+        <v>2.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.16</v>
+        <v>4.72</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S46" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="T46" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="U46" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>2.76</v>
+        <v>3.96</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.08</v>
+        <v>1.95</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,62 +6603,62 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.09</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="O48" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="P48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q48" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T48" t="n">
+      <c r="Z48" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC48" t="n">
         <v>2.19</v>
       </c>
-      <c r="U48" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X48" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45925.66666666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>9.5</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="N49" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,62 +6861,62 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="M50" t="n">
-        <v>3.29</v>
+        <v>3.78</v>
       </c>
       <c r="N50" t="n">
         <v>4.7</v>
       </c>
       <c r="O50" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X50" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD50" t="n">
         <v>2.25</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AE50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.77083333334</v>
+        <v>45925.875</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W51" t="n">
         <v>1.35</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N51" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>8</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X51" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.57</v>
+        <v>1.99</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AH51" t="n">
-        <v>3.04</v>
+        <v>1.8</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.89583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.79</v>
+        <v>3.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N52" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
-        <v>2.72</v>
+        <v>4.35</v>
       </c>
       <c r="P52" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.92</v>
+        <v>2.92</v>
       </c>
       <c r="R52" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="T52" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U52" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="X52" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="Y52" t="n">
         <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AA52" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.89583333334</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>2.87</v>
       </c>
       <c r="N53" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,522 +7327,6 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45925.85416666666</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Guabirá</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="N54" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X54" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="3" t="n">
-        <v>45925.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>South America Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Estudiantes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O55" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" s="3" t="n">
-        <v>45925.89583333334</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X56" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="3" t="n">
-        <v>45925.89583333334</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>2.05</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.04</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AC26" t="n">
         <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.41</v>
       </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X27" t="n">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC27" t="n">
         <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.41</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X29" t="n">
-        <v>4.3</v>
+        <v>3.36</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.64</v>
+        <v>1.96</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>2.14</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.14</v>
+        <v>5.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>4.47</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.93</v>
+        <v>2.01</v>
       </c>
       <c r="P32" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.09</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.51</v>
+        <v>3.66</v>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>4.8</v>
       </c>
       <c r="O33" t="n">
-        <v>3.17</v>
+        <v>2.23</v>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="T33" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.16</v>
       </c>
-      <c r="X33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="P34" t="n">
         <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>4.52</v>
       </c>
       <c r="R34" t="n">
         <v>1.3</v>
@@ -4821,37 +4821,37 @@
         <v>3.22</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
         <v>4.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AA34" t="n">
         <v>2.73</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
         <v>1.64</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4867,13 +4867,13 @@
         <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X35" t="n">
         <v>4.8</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="Y35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.33</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.02</v>
+        <v>5.86</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>1.44</v>
       </c>
       <c r="O36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.86</v>
+        <v>2.02</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="N3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.7</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>2.6</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -834,25 +834,25 @@
         <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" t="n">
         <v>1.83</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>4.35</v>
+        <v>3.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AA7" t="n">
         <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45925.4375</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45925.4375</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="O13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45925.50694444445</v>
+        <v>45925.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45925.51041666666</v>
+        <v>45925.50694444445</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>5.68</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45925.51736111111</v>
+        <v>45925.51041666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>5.68</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45925.52083333334</v>
+        <v>45925.51736111111</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,49 +2604,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>11</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2677,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45925.53125</v>
+        <v>45925.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45925.53472222222</v>
+        <v>45925.53125</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.53472222222</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.82</v>
+        <v>3.85</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,62 +3378,62 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="P23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="M24" t="n">
         <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.47</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S25" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y25" t="n">
         <v>2.5</v>
       </c>
-      <c r="T25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="N26" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.89</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
         <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AB26" t="n">
         <v>1.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.12</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45925.5625</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.87</v>
+        <v>3.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="T28" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="Y28" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45925.5625</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
       <c r="P29" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.85</v>
+        <v>2.61</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X29" t="n">
-        <v>3.36</v>
+        <v>2.97</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.14</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>5.25</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.48</v>
+        <v>3.58</v>
       </c>
       <c r="O31" t="n">
-        <v>5.1</v>
+        <v>2.33</v>
       </c>
       <c r="P31" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.95</v>
+        <v>4.52</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V31" t="n">
         <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X31" t="n">
-        <v>4.63</v>
+        <v>4.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.41</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="N32" t="n">
-        <v>6</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R32" t="n">
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.28</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X32" t="n">
-        <v>4.3</v>
+        <v>3.36</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>3.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="N33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X33" t="n">
         <v>4.8</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="Y33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.33</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="M34" t="n">
         <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="N35" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3.17</v>
+        <v>2.23</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="T35" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U35" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.86</v>
+        <v>1.41</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>4.47</v>
       </c>
       <c r="N36" t="n">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,19 +5122,19 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="O38" t="n">
-        <v>2.83</v>
+        <v>5.85</v>
       </c>
       <c r="P38" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.52</v>
+        <v>1.95</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
         <v>3.84</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,19 +5380,19 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,86 +5571,86 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.6</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>1.46</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>2.83</v>
       </c>
       <c r="P40" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.22</v>
+        <v>3.54</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S40" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="T40" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="U40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.31</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>2.33</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45925.65625</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.53</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="O42" t="n">
-        <v>3.7</v>
+        <v>5.93</v>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R42" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="S42" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="T42" t="n">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="U42" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="X42" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC42" t="n">
         <v>2.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,22 +5958,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6009,10 +6009,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45925.65625</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.66666666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>11</v>
+        <v>3.09</v>
       </c>
       <c r="M45" t="n">
-        <v>6.7</v>
+        <v>3.09</v>
       </c>
       <c r="N45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R45" t="n">
         <v>1.23</v>
       </c>
-      <c r="O45" t="n">
-        <v>7</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S45" t="n">
-        <v>4.3</v>
+        <v>3.56</v>
       </c>
       <c r="T45" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="U45" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W45" t="n">
         <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,19 +6283,19 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.66</v>
+        <v>11</v>
       </c>
       <c r="M46" t="n">
-        <v>3.29</v>
+        <v>6.7</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>1.23</v>
       </c>
       <c r="O46" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="P46" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.72</v>
+        <v>1.64</v>
       </c>
       <c r="R46" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>3.96</v>
+        <v>6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.95</v>
+        <v>1.06</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.77083333334</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,86 +6474,86 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="M47" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N47" t="n">
-        <v>9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.95</v>
       </c>
-      <c r="P47" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>8</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S47" t="n">
+      <c r="AI47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>2.5</v>
       </c>
-      <c r="T47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="48">
@@ -6615,31 +6615,31 @@
         <v>2.62</v>
       </c>
       <c r="P48" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q48" t="n">
         <v>4.07</v>
       </c>
       <c r="R48" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S48" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T48" t="n">
         <v>3.5</v>
       </c>
       <c r="U48" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V48" t="n">
         <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X48" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="Y48" t="n">
         <v>2.35</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,19 +6799,19 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="O50" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.875</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,86 +6990,86 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="M51" t="n">
-        <v>3.23</v>
+        <v>3.78</v>
       </c>
       <c r="N51" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O51" t="n">
-        <v>2.48</v>
+        <v>1.99</v>
       </c>
       <c r="P51" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.45</v>
+        <v>5.07</v>
       </c>
       <c r="R51" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>2.62</v>
+        <v>3.56</v>
       </c>
       <c r="T51" t="n">
-        <v>3.22</v>
+        <v>2.19</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
-        <v>2.75</v>
+        <v>4.85</v>
       </c>
       <c r="Y51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z51" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA51" t="n">
-        <v>3.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB51" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC51" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH51" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.875</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.33</v>
+        <v>1.74</v>
       </c>
       <c r="M52" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
-        <v>4.35</v>
+        <v>2.57</v>
       </c>
       <c r="P52" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S52" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="T52" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U52" t="n">
         <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X52" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,85 +7248,214 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.17</v>
+        <v>3.33</v>
       </c>
       <c r="M53" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="N53" t="n">
-        <v>3.23</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="P53" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>2.92</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S53" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="T53" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
         <v>1.3</v>
       </c>
       <c r="V53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V54" t="n">
         <v>1.09</v>
       </c>
-      <c r="W53" t="n">
+      <c r="W54" t="n">
         <v>1.5</v>
       </c>
-      <c r="X53" t="n">
+      <c r="X54" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y54" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="Z54" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AA54" t="n">
         <v>4.22</v>
       </c>
-      <c r="AB53" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC53" t="n">
+      <c r="AB54" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC54" t="n">
         <v>1.99</v>
       </c>
-      <c r="AD53" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH53" t="n">
+      <c r="AD54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="3" t="n">
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -669,49 +669,49 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
         <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA2" t="n">
         <v>3.48</v>
@@ -723,7 +723,7 @@
         <v>1.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
         <v>1.95</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
         <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.39</v>
+        <v>3.64</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>2.1</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.95</v>
+        <v>7.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.5</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45925.4375</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>4.95</v>
       </c>
       <c r="O9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.95</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45925.4375</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
         <v>1.4</v>
@@ -1863,25 +1863,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X11" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.05</v>
+        <v>3.22</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD11" t="n">
         <v>2.02</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" t="n">
         <v>2.38</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45925.5</v>
@@ -2220,25 +2220,25 @@
         <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
         <v>2.72</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="T14" t="n">
         <v>2.55</v>
@@ -2250,10 +2250,10 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>3.28</v>
+        <v>3.57</v>
       </c>
       <c r="Y14" t="n">
         <v>1.94</v>
@@ -2262,16 +2262,16 @@
         <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45925.50694444445</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45925.51041666666</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>5.68</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.06</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="T16" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>4.53</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,13 +2545,13 @@
         <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45925.51736111111</v>
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="N17" t="n">
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>13.9</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
         <v>1.33</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="O18" t="n">
         <v>2.05</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.84</v>
+        <v>3.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X25" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>3.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>3.34</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>2.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>4.84</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="V26" t="n">
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.72</v>
+        <v>4.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.99</v>
+        <v>2.49</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>5.7</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
-        <v>1.92</v>
+        <v>2.95</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.29</v>
+        <v>3.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="T27" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45925.5625</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.96</v>
+        <v>6.29</v>
       </c>
       <c r="R28" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AA28" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45925.5625</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="N30" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
-        <v>5.1</v>
+        <v>2.23</v>
       </c>
       <c r="P30" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.53</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>1.44</v>
+        <v>2.62</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4410,19 +4410,19 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
         <v>4.52</v>
@@ -4434,37 +4434,37 @@
         <v>3.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
         <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AA31" t="n">
         <v>2.73</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
         <v>1.97</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4542,59 +4542,59 @@
         <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.93</v>
+        <v>2.72</v>
       </c>
       <c r="P32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.09</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="AB32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2.75</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
         <v>1.54</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
         <v>3.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
         <v>2.41</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
         <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.28</v>
+        <v>2.71</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI33" t="n">
         <v>2.1</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.62</v>
+        <v>5.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>2.23</v>
+        <v>5.69</v>
       </c>
       <c r="P35" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.33</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AC35" t="n">
         <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.62</v>
+        <v>1.44</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S37" t="n">
         <v>3.1</v>
       </c>
-      <c r="N37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T37" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="U37" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>3.84</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.42</v>
+        <v>1.72</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.78</v>
+        <v>1.06</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>2.08</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="N38" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.44</v>
       </c>
-      <c r="O38" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.18</v>
       </c>
-      <c r="X38" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AC38" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.06</v>
+        <v>1.82</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.1</v>
+        <v>2.23</v>
       </c>
       <c r="M39" t="n">
-        <v>9.5</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>16.5</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>1.31</v>
+        <v>2.86</v>
       </c>
       <c r="P39" t="n">
-        <v>3.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>13.82</v>
+        <v>3.54</v>
       </c>
       <c r="R39" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.88</v>
+        <v>2.52</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>6.22</v>
+        <v>3.84</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>1.35</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.54</v>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45925.625</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,62 +5571,62 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>1.09</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>16</v>
       </c>
       <c r="O40" t="n">
-        <v>2.83</v>
+        <v>1.35</v>
       </c>
       <c r="P40" t="n">
-        <v>2.12</v>
+        <v>3.29</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.54</v>
+        <v>12</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="T40" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="U40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X40" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.45</v>
       </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.61</v>
+        <v>9.25</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45925.625</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>1.71</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>1.6</v>
+        <v>4.35</v>
       </c>
       <c r="O42" t="n">
-        <v>5.93</v>
+        <v>2.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>2.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,22 +5958,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6009,10 +6009,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45925.65625</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45925.65625</v>
@@ -6348,31 +6348,31 @@
         <v>11</v>
       </c>
       <c r="M46" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="N46" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="O46" t="n">
-        <v>7</v>
+        <v>6.47</v>
       </c>
       <c r="P46" t="n">
         <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -6384,22 +6384,22 @@
         <v>6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6418,10 +6418,10 @@
         <v>1.06</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45925.6875</v>
@@ -6603,22 +6603,22 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="N48" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="P48" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.07</v>
+        <v>4.97</v>
       </c>
       <c r="R48" t="n">
         <v>1.58</v>
@@ -6633,19 +6633,19 @@
         <v>1.24</v>
       </c>
       <c r="V48" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X48" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AA48" t="n">
         <v>5.25</v>
@@ -6657,7 +6657,7 @@
         <v>2.19</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45925.79166666666</v>
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="M50" t="n">
-        <v>3.55</v>
+        <v>3.81</v>
       </c>
       <c r="N50" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,16 +6928,16 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45925.85416666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.74</v>
+        <v>3.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
-        <v>2.57</v>
+        <v>4.35</v>
       </c>
       <c r="P52" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="R52" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="T52" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U52" t="n">
         <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X52" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AA52" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC52" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.33</v>
+        <v>1.93</v>
       </c>
       <c r="M53" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.35</v>
+        <v>2.55</v>
       </c>
       <c r="P53" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.92</v>
+        <v>4.91</v>
       </c>
       <c r="R53" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="T53" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U53" t="n">
         <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
         <v>1.42</v>
       </c>
       <c r="X53" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,16 +7315,16 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7377,19 +7377,19 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="M54" t="n">
-        <v>2.87</v>
+        <v>3.21</v>
       </c>
       <c r="N54" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>2.77</v>
       </c>
       <c r="P54" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q54" t="n">
         <v>4.08</v>
@@ -7401,7 +7401,7 @@
         <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U54" t="n">
         <v>1.3</v>
@@ -7410,25 +7410,25 @@
         <v>1.09</v>
       </c>
       <c r="W54" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X54" t="n">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AA54" t="n">
         <v>4.22</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AD54" t="n">
         <v>1.8</v>
@@ -7450,10 +7450,10 @@
         <v>1.62</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45925.89930555555</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="M5" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45925.42708333334</v>
@@ -1314,77 +1314,77 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
         <v>1.4</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.54</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.949999999999999</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="T8" t="n">
         <v>3.3</v>
@@ -1473,22 +1473,22 @@
         <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
         <v>1.17</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AI8" t="n">
         <v>1.4</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>5.69</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1611,10 +1611,10 @@
         <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AA9" t="n">
         <v>3.28</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
         <v>2.12</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45925.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.38</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45925.5</v>
@@ -2604,55 +2604,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.9</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
         <v>3.08</v>
@@ -2674,7 +2674,7 @@
         <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AI17" t="n">
         <v>1.33</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="O18" t="n">
         <v>2.05</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.9</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.89</v>
-      </c>
       <c r="Z23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AI23" t="n">
         <v>1.95</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,28 +3507,28 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Q24" t="n">
-        <v>3.96</v>
+        <v>3.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
         <v>3.1</v>
@@ -3540,28 +3540,28 @@
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>3.64</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S25" t="n">
         <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.12</v>
       </c>
-      <c r="M26" t="n">
+      <c r="Q26" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.04</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.42</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,13 +3835,13 @@
         <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="M27" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.1</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.35</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X27" t="n">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45925.5625</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1.55</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AA28" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45925.5625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>7.1</v>
       </c>
       <c r="O29" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="P29" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.6</v>
+        <v>6.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45925.5625</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.62</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.33</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH30" t="n">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="O31" t="n">
-        <v>2.34</v>
+        <v>3.17</v>
       </c>
       <c r="P31" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.52</v>
+        <v>2.41</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.18</v>
+        <v>2.71</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.88</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.3</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AH32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI32" t="n">
         <v>2.75</v>
       </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="O33" t="n">
-        <v>3.17</v>
+        <v>2.23</v>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.41</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="U33" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.71</v>
+        <v>1.97</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.88</v>
+        <v>1.16</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>4.52</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="T34" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="U34" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.23</v>
       </c>
-      <c r="X34" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.2</v>
+        <v>1.41</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>4.47</v>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>5.69</v>
+        <v>2.01</v>
       </c>
       <c r="P35" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
         <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T35" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U35" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>4.63</v>
+        <v>4.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.44</v>
+        <v>2.87</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.01</v>
+        <v>2.72</v>
       </c>
       <c r="P36" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="T36" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="U36" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>4.3</v>
+        <v>5.65</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AD36" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>2.03</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.09</v>
       </c>
       <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
+      <c r="R37" t="n">
         <v>1.44</v>
       </c>
-      <c r="O37" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.51</v>
+        <v>3.41</v>
       </c>
       <c r="U37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.44</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X37" t="n">
-        <v>3.84</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.06</v>
+        <v>1.78</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.08</v>
+        <v>6.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.11</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.14</v>
+        <v>1.47</v>
       </c>
       <c r="O38" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="R38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.71</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>1.82</v>
       </c>
       <c r="M41" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.33</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
-        <v>3.84</v>
+        <v>2.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45925.65625</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.71</v>
+        <v>2.53</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="N42" t="n">
-        <v>4.35</v>
+        <v>2.78</v>
       </c>
       <c r="O42" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6087,31 +6087,31 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="N44" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="O44" t="n">
-        <v>5.93</v>
+        <v>6.79</v>
       </c>
       <c r="P44" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R44" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="T44" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U44" t="n">
         <v>1.28</v>
@@ -6120,28 +6120,28 @@
         <v>1.04</v>
       </c>
       <c r="W44" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X44" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA44" t="n">
         <v>4.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AI44" t="n">
         <v>3.1</v>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M46" t="n">
         <v>6.75</v>
@@ -6354,25 +6354,25 @@
         <v>1.12</v>
       </c>
       <c r="O46" t="n">
-        <v>6.47</v>
+        <v>7.5</v>
       </c>
       <c r="P46" t="n">
         <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U46" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -6381,25 +6381,25 @@
         <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA46" t="n">
         <v>2.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
         <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>1.13</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AI46" t="n">
         <v>3.5</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="M48" t="n">
-        <v>2.99</v>
+        <v>3.72</v>
       </c>
       <c r="N48" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>8</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA48" t="n">
         <v>3.9</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AB48" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.19</v>
+        <v>2.57</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.77</v>
+        <v>3.04</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45925.79166666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>2.9</v>
       </c>
       <c r="N49" t="n">
-        <v>9.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="O49" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>4.07</v>
       </c>
       <c r="R49" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Z49" t="n">
         <v>1.44</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA49" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.57</v>
+        <v>2.37</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>3.04</v>
+        <v>1.74</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AJ49" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45925.79166666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.33</v>
+        <v>1.95</v>
       </c>
       <c r="M52" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="O52" t="n">
-        <v>4.35</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
         <v>1.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V52" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W52" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X52" t="n">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.93</v>
+        <v>3.33</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N53" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
-        <v>2.55</v>
+        <v>4.35</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.91</v>
+        <v>2.92</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S53" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="T53" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
         <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W53" t="n">
         <v>1.42</v>
       </c>
       <c r="X53" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AA53" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,16 +7315,16 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7377,40 +7377,40 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="M54" t="n">
         <v>3.21</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O54" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="P54" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="R54" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
         <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V54" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X54" t="n">
         <v>2.71</v>
@@ -7419,19 +7419,19 @@
         <v>2.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="AB54" t="n">
         <v>1.22</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AI54" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -669,31 +669,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="M2" t="n">
         <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U2" t="n">
         <v>1.33</v>
@@ -702,19 +702,19 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
         <v>2.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AB2" t="n">
         <v>1.22</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" t="n">
         <v>1.83</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O4" t="n">
         <v>3.4</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.64</v>
-      </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="Y4" t="n">
         <v>1.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI4" t="n">
         <v>2.1</v>
@@ -1323,22 +1323,22 @@
         <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
         <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
         <v>1.46</v>
@@ -1359,16 +1359,16 @@
         <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AI7" t="n">
         <v>2</v>
@@ -1464,7 +1464,7 @@
         <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="T8" t="n">
         <v>3.3</v>
@@ -1476,7 +1476,7 @@
         <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
         <v>2.55</v>
@@ -1491,7 +1491,7 @@
         <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
         <v>2.51</v>
@@ -1587,7 +1587,7 @@
         <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.69</v>
+        <v>5.45</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1626,7 +1626,7 @@
         <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
         <v>2.12</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
         <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="R11" t="n">
         <v>1.36</v>
@@ -1854,37 +1854,37 @@
         <v>2.89</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -2088,28 +2088,28 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="P13" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
         <v>2.29</v>
@@ -2118,31 +2118,31 @@
         <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
         <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>4.5</v>
+        <v>5.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AI13" t="n">
         <v>1.66</v>
@@ -2223,55 +2223,55 @@
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
         <v>2.72</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="T14" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>3.57</v>
+        <v>3.28</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Z14" t="n">
         <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AI14" t="n">
         <v>1.93</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
@@ -2370,37 +2370,37 @@
         <v>3.22</v>
       </c>
       <c r="T15" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
         <v>1.47</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
         <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
         <v>2.59</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.96</v>
+        <v>3.21</v>
       </c>
       <c r="AI15" t="n">
         <v>1.18</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
@@ -2484,68 +2484,68 @@
         <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="T16" t="n">
         <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
         <v>1.54</v>
       </c>
       <c r="Z16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI16" t="n">
         <v>1.53</v>
@@ -2613,34 +2613,34 @@
         <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="P17" t="n">
         <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>12.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
         <v>2.25</v>
@@ -2649,16 +2649,16 @@
         <v>1.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AB17" t="n">
         <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
         <v>3.08</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.93</v>
       </c>
       <c r="N21" t="n">
-        <v>2.23</v>
+        <v>1.58</v>
       </c>
       <c r="O21" t="n">
-        <v>3.49</v>
+        <v>4.29</v>
       </c>
       <c r="P21" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.73</v>
+        <v>2.21</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>3.68</v>
+        <v>4.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.78</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>4.29</v>
+        <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.21</v>
+        <v>4.82</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>2.23</v>
       </c>
       <c r="T22" t="n">
-        <v>2.14</v>
+        <v>3.74</v>
       </c>
       <c r="U22" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="X22" t="n">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.07</v>
+        <v>1.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.44</v>
+        <v>2.23</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3390,31 +3390,31 @@
         <v>2.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="R23" t="n">
         <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
         <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="Y23" t="n">
         <v>1.9</v>
@@ -3429,10 +3429,10 @@
         <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" t="n">
         <v>1.95</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>3.64</v>
       </c>
       <c r="O24" t="n">
-        <v>3.51</v>
+        <v>2.99</v>
       </c>
       <c r="P24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N25" t="n">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="O25" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="U25" t="n">
         <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X25" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
         <v>1.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>3.47</v>
+        <v>2.66</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>3.51</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.13</v>
+        <v>3.24</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="U26" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X26" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3903,7 +3903,7 @@
         <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="P27" t="n">
         <v>2.03</v>
@@ -3912,13 +3912,13 @@
         <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
         <v>2.61</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U27" t="n">
         <v>1.33</v>
@@ -3930,7 +3930,7 @@
         <v>1.36</v>
       </c>
       <c r="X27" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="Y27" t="n">
         <v>1.9</v>
@@ -3945,10 +3945,10 @@
         <v>1.29</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" t="n">
         <v>1.61</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.34</v>
+        <v>7.1</v>
       </c>
       <c r="O28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
         <v>2.65</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.43</v>
-      </c>
       <c r="T28" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45925.5625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>2.03</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>7.1</v>
+        <v>3.47</v>
       </c>
       <c r="O29" t="n">
-        <v>2.13</v>
+        <v>2.68</v>
       </c>
       <c r="P29" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y29" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45925.5625</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="O30" t="n">
-        <v>2.62</v>
+        <v>5.74</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>4.11</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.56</v>
+        <v>1.12</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.95</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.66</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.48</v>
       </c>
-      <c r="O32" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.6</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>4.63</v>
+        <v>4.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>4.47</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.34</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.52</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.41</v>
+        <v>3.09</v>
       </c>
       <c r="M35" t="n">
-        <v>4.47</v>
+        <v>3.51</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="O35" t="n">
-        <v>2.01</v>
+        <v>3.84</v>
       </c>
       <c r="P35" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.28</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z35" t="n">
+      <c r="AI35" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5058,58 +5058,58 @@
         <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="P36" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="R36" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>3.88</v>
+        <v>2.77</v>
       </c>
       <c r="T36" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="U36" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="X36" t="n">
-        <v>5.65</v>
+        <v>3.44</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.59</v>
+        <v>1.92</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.09</v>
+        <v>2.87</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="M37" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="N37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
         <v>2.71</v>
@@ -5199,10 +5199,10 @@
         <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S37" t="n">
         <v>2.5</v>
@@ -5211,10 +5211,10 @@
         <v>3.41</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
         <v>1.44</v>
@@ -5226,19 +5226,19 @@
         <v>2.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
         <v>4.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC37" t="n">
         <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH37" t="n">
         <v>1.78</v>
@@ -5322,34 +5322,34 @@
         <v>1.47</v>
       </c>
       <c r="O38" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R38" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="S38" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="T38" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X38" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="Y38" t="n">
         <v>1.68</v>
@@ -5358,16 +5358,16 @@
         <v>2.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.14</v>
+        <v>2.76</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI38" t="n">
         <v>2.87</v>
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
         <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
         <v>2.86</v>
@@ -5457,7 +5457,7 @@
         <v>2.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="R39" t="n">
         <v>1.32</v>
@@ -5466,28 +5466,28 @@
         <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="U39" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V39" t="n">
         <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X39" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB39" t="n">
         <v>1.35</v>
@@ -5496,7 +5496,7 @@
         <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>1.27</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
         <v>1.81</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="M40" t="n">
         <v>7.75</v>
@@ -5580,52 +5580,52 @@
         <v>16</v>
       </c>
       <c r="O40" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="P40" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R40" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="T40" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="U40" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>6.75</v>
+        <v>5.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z40" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA40" t="n">
         <v>1.93</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AH40" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AI40" t="n">
         <v>1.11</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.53</v>
+        <v>2.02</v>
       </c>
       <c r="M42" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>3.56</v>
       </c>
       <c r="O42" t="n">
-        <v>3.8</v>
+        <v>2.79</v>
       </c>
       <c r="P42" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>4.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="T42" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U42" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V42" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="X42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>2.37</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.9</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.02</v>
+        <v>2.53</v>
       </c>
       <c r="M43" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q43" t="n">
         <v>3.1</v>
       </c>
-      <c r="N43" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45925.65625</v>
@@ -6096,7 +6096,7 @@
         <v>1.46</v>
       </c>
       <c r="O44" t="n">
-        <v>6.79</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
         <v>2.03</v>
@@ -6138,7 +6138,7 @@
         <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD44" t="n">
         <v>1.53</v>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AI44" t="n">
         <v>3.1</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M46" t="n">
         <v>6.75</v>
       </c>
       <c r="N46" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="O46" t="n">
         <v>7.5</v>
@@ -6360,19 +6360,19 @@
         <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="T46" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U46" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -6381,25 +6381,25 @@
         <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="Y46" t="n">
         <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
         <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,19 +6732,19 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O49" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="P49" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q49" t="n">
         <v>4.07</v>
@@ -6753,40 +6753,40 @@
         <v>1.55</v>
       </c>
       <c r="S49" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T49" t="n">
         <v>3.5</v>
       </c>
       <c r="U49" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V49" t="n">
         <v>1.08</v>
       </c>
       <c r="W49" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X49" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="AB49" t="n">
         <v>1.12</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AI49" t="n">
         <v>1.8</v>
@@ -6861,77 +6861,77 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="M50" t="n">
-        <v>3.81</v>
+        <v>3.97</v>
       </c>
       <c r="N50" t="n">
-        <v>3.35</v>
+        <v>4.66</v>
       </c>
       <c r="O50" t="n">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="P50" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="R50" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S50" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="T50" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="U50" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
         <v>1.18</v>
       </c>
-      <c r="X50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AI50" t="n">
         <v>1.57</v>
@@ -7029,10 +7029,10 @@
         <v>4.85</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AA51" t="n">
         <v>2.15</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.95</v>
+        <v>3.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N52" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>4.35</v>
       </c>
       <c r="P52" t="n">
         <v>1.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="T52" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U52" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
         <v>1.36</v>
       </c>
-      <c r="X52" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH52" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.33</v>
+        <v>1.74</v>
       </c>
       <c r="M53" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4.35</v>
+        <v>2.55</v>
       </c>
       <c r="P53" t="n">
         <v>1.92</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.92</v>
+        <v>4.91</v>
       </c>
       <c r="R53" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="T53" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U53" t="n">
         <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X53" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,16 +7315,16 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI53" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="M54" t="n">
-        <v>3.21</v>
+        <v>2.87</v>
       </c>
       <c r="N54" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="O54" t="n">
         <v>2.88</v>
@@ -7392,46 +7392,46 @@
         <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T54" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="U54" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
         <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X54" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC54" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AI54" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK54"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,17 +655,17 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -732,7 +732,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
         <v>3.4</v>
@@ -942,46 +942,46 @@
         <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
         <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
         <v>3.34</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>2.1</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>5.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45925.4375</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>2.51</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.79</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.12</v>
+        <v>2.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45925.4375</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45925.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.05</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.52</v>
-      </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45925.5</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.82</v>
+        <v>4.13</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>3.74</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>2.25</v>
+        <v>3.34</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.25</v>
+        <v>2.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,19 +3316,19 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,43 +3378,43 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="Y23" t="n">
         <v>1.9</v>
@@ -3423,16 +3423,16 @@
         <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.64</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
-        <v>2.99</v>
+        <v>3.51</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="T24" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="U24" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,13 +3577,13 @@
         <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.04</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.35</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.45</v>
+        <v>3.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="M26" t="n">
         <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="O26" t="n">
-        <v>3.51</v>
+        <v>2.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.24</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
         <v>1.47</v>
@@ -3789,37 +3789,37 @@
         <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.99</v>
+        <v>2.49</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3.33</v>
+        <v>3.03</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="O27" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
-        <v>2.61</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45925.5625</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>3.47</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="P29" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.26</v>
+        <v>3.74</v>
       </c>
       <c r="R29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.43</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.31</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.68</v>
+        <v>2.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
         <v>1.9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
         <v>4.1</v>
       </c>
-      <c r="N30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="O30" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="Y30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.25</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.12</v>
+        <v>2.12</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="M31" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
         <v>3.7</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.94</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
-        <v>5.88</v>
+        <v>5.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,13 +4480,13 @@
         <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="M32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S32" t="n">
         <v>3.5</v>
       </c>
-      <c r="N32" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T32" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="U32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.48</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI32" t="n">
         <v>2.75</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="O35" t="n">
-        <v>3.84</v>
+        <v>2.85</v>
       </c>
       <c r="P35" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="U35" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="V35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,86 +5055,86 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="M36" t="n">
-        <v>3.19</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.69</v>
+        <v>1.47</v>
       </c>
       <c r="O36" t="n">
+        <v>7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T36" t="n">
         <v>2.58</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U36" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X36" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AA36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.87</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="37">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.4</v>
+        <v>1.07</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>7.75</v>
       </c>
       <c r="N38" t="n">
-        <v>1.47</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>1.43</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>3.04</v>
+        <v>3.88</v>
       </c>
       <c r="T38" t="n">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
       <c r="U38" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>3.58</v>
+        <v>5.9</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,19 +5380,19 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.87</v>
+        <v>1.11</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.44</v>
+        <v>5.75</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="39">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="M40" t="n">
-        <v>7.75</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>16</v>
+        <v>3.56</v>
       </c>
       <c r="O40" t="n">
-        <v>1.43</v>
+        <v>2.79</v>
       </c>
       <c r="P40" t="n">
-        <v>3.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>9.640000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="R40" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>3.88</v>
+        <v>2.43</v>
       </c>
       <c r="T40" t="n">
-        <v>2.04</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X40" t="n">
-        <v>5.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.83</v>
+        <v>1.62</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.81</v>
+        <v>1.15</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,19 +5638,19 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>9</v>
+        <v>1.61</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>5.75</v>
+        <v>2.37</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.82</v>
+        <v>2.53</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S41" t="n">
         <v>2.4</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45925.65625</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.32</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>2.62</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>2.37</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.53</v>
+        <v>6.6</v>
       </c>
       <c r="M43" t="n">
-        <v>2.91</v>
+        <v>3.82</v>
       </c>
       <c r="N43" t="n">
-        <v>2.78</v>
+        <v>1.46</v>
       </c>
       <c r="O43" t="n">
-        <v>4.22</v>
+        <v>6</v>
       </c>
       <c r="P43" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="Q43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI43" t="n">
         <v>3.1</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ43" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45925.65625</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6.6</v>
+        <v>3.09</v>
       </c>
       <c r="M44" t="n">
-        <v>3.82</v>
+        <v>3.09</v>
       </c>
       <c r="N44" t="n">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>3.02</v>
       </c>
       <c r="P44" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="R44" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
-        <v>2.43</v>
+        <v>3.56</v>
       </c>
       <c r="T44" t="n">
-        <v>3.22</v>
+        <v>2.19</v>
       </c>
       <c r="U44" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>2.59</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AB44" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC44" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,19 +6154,19 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI44" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.53</v>
+        <v>2.01</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.09</v>
+        <v>11</v>
       </c>
       <c r="M45" t="n">
-        <v>3.09</v>
+        <v>6.75</v>
       </c>
       <c r="N45" t="n">
-        <v>2.12</v>
+        <v>1.22</v>
       </c>
       <c r="O45" t="n">
-        <v>3.02</v>
+        <v>7.5</v>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.77</v>
+        <v>1.67</v>
       </c>
       <c r="R45" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S45" t="n">
-        <v>3.56</v>
+        <v>4.15</v>
       </c>
       <c r="T45" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="U45" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="V45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W45" t="n">
         <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,19 +6283,19 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.01</v>
+        <v>1.28</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.66666666666</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>11</v>
+        <v>1.66</v>
       </c>
       <c r="M46" t="n">
-        <v>6.75</v>
+        <v>3.29</v>
       </c>
       <c r="N46" t="n">
-        <v>1.22</v>
+        <v>4.7</v>
       </c>
       <c r="O46" t="n">
-        <v>7.5</v>
+        <v>2.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q46" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Y46" t="n">
         <v>1.67</v>
       </c>
-      <c r="R46" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S46" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X46" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.35</v>
-      </c>
       <c r="Z46" t="n">
-        <v>2.86</v>
+        <v>2.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,19 +6412,19 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.05</v>
+        <v>1.95</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="M47" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="N47" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O47" t="n">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="P47" t="n">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.72</v>
+        <v>4.07</v>
       </c>
       <c r="R47" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="T47" t="n">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="X47" t="n">
-        <v>3.96</v>
+        <v>2.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.49</v>
+        <v>4.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.61</v>
+        <v>2.19</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,19 +6541,19 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.77083333334</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="48">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,86 +6732,86 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="N49" t="n">
-        <v>4.3</v>
+        <v>5.05</v>
       </c>
       <c r="O49" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="P49" t="n">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.07</v>
+        <v>4.75</v>
       </c>
       <c r="R49" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="S49" t="n">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="T49" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="U49" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="V49" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="X49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH49" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y49" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AI49" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="M50" t="n">
-        <v>3.97</v>
+        <v>3.78</v>
       </c>
       <c r="N50" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="O50" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="P50" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.2</v>
+        <v>5.07</v>
       </c>
       <c r="R50" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S50" t="n">
-        <v>3.15</v>
+        <v>3.56</v>
       </c>
       <c r="T50" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="U50" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="X50" t="n">
-        <v>3.7</v>
+        <v>4.85</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,19 +6928,19 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.875</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.56</v>
+        <v>3.33</v>
       </c>
       <c r="M51" t="n">
-        <v>3.78</v>
+        <v>2.88</v>
       </c>
       <c r="N51" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>1.99</v>
+        <v>4.35</v>
       </c>
       <c r="P51" t="n">
-        <v>2.47</v>
+        <v>1.92</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.07</v>
+        <v>2.92</v>
       </c>
       <c r="R51" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="S51" t="n">
-        <v>3.56</v>
+        <v>2.51</v>
       </c>
       <c r="T51" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="U51" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W51" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="X51" t="n">
-        <v>4.85</v>
+        <v>2.56</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.29</v>
+        <v>1.58</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,19 +7057,19 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.875</v>
+        <v>45925.89583333334</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.33</v>
+        <v>1.74</v>
       </c>
       <c r="M52" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
-        <v>4.35</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
         <v>1.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.92</v>
+        <v>4.91</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="T52" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
         <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X52" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,22 +7248,22 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="M53" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N53" t="n">
         <v>3.23</v>
       </c>
-      <c r="N53" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O53" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="P53" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.91</v>
+        <v>3.9</v>
       </c>
       <c r="R53" t="n">
         <v>1.45</v>
@@ -7272,7 +7272,7 @@
         <v>2.56</v>
       </c>
       <c r="T53" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U53" t="n">
         <v>1.3</v>
@@ -7281,28 +7281,28 @@
         <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X53" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB53" t="n">
         <v>1.16</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,147 +7315,18 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45925.89583333334</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>45925</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Chapecoense</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N54" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK54" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45925.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.72</v>
+        <v>2.57</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45925.5</v>
@@ -3150,7 +3150,7 @@
         <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T24" t="n">
         <v>3.04</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.18</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.84</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N25" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="O25" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="T25" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X25" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="Y25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="M26" t="n">
         <v>3.04</v>
       </c>
       <c r="N26" t="n">
-        <v>3.34</v>
+        <v>2.66</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>3.51</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>3.24</v>
       </c>
       <c r="R26" t="n">
         <v>1.47</v>
@@ -3789,37 +3789,37 @@
         <v>2.43</v>
       </c>
       <c r="T26" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X26" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.49</v>
+        <v>1.99</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.58</v>
+        <v>3.94</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.74</v>
+        <v>2.38</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="X29" t="n">
-        <v>3.44</v>
+        <v>5.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.5</v>
       </c>
-      <c r="N30" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.52</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.09</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>3.51</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.96</v>
+        <v>4.05</v>
       </c>
       <c r="O31" t="n">
-        <v>3.84</v>
+        <v>2.36</v>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,28 +4539,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>4.47</v>
       </c>
       <c r="N32" t="n">
-        <v>1.45</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>5.74</v>
+        <v>2.01</v>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T32" t="n">
         <v>2.34</v>
@@ -4569,31 +4569,31 @@
         <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AC32" t="n">
         <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.44</v>
+        <v>2.87</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>4.8</v>
+        <v>2.33</v>
       </c>
       <c r="O33" t="n">
-        <v>2.23</v>
+        <v>2.85</v>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>3.04</v>
+        <v>3.86</v>
       </c>
       <c r="T33" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>3.58</v>
+        <v>5.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.04</v>
+        <v>1.46</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="M34" t="n">
-        <v>4.47</v>
+        <v>3.66</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="O34" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="T34" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="U34" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X34" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,62 +4926,62 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O35" t="n">
-        <v>2.85</v>
+        <v>5.95</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="U35" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>5.6</v>
+        <v>4.86</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>6.4</v>
+        <v>2.02</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="N36" t="n">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>2.71</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.85</v>
+        <v>5.05</v>
       </c>
       <c r="R36" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="T36" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="U36" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W36" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="X36" t="n">
-        <v>3.58</v>
+        <v>2.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AC36" t="n">
         <v>2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>2.76</v>
+        <v>1.34</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.11</v>
+        <v>4.33</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>1.38</v>
       </c>
       <c r="O37" t="n">
-        <v>2.71</v>
+        <v>7</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.05</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3.41</v>
+        <v>2.58</v>
       </c>
       <c r="U37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.3</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.18</v>
       </c>
       <c r="AC37" t="n">
         <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.76</v>
+        <v>2.87</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.71</v>
+        <v>1.44</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,22 +5571,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="N40" t="n">
-        <v>3.56</v>
+        <v>1.46</v>
       </c>
       <c r="O40" t="n">
-        <v>2.79</v>
+        <v>6</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.32</v>
+        <v>2.1</v>
       </c>
       <c r="R40" t="n">
         <v>1.47</v>
@@ -5595,37 +5595,37 @@
         <v>2.43</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U40" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V40" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X40" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.61</v>
+        <v>1.06</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45925.65625</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.53</v>
+        <v>2.02</v>
       </c>
       <c r="M41" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>3.56</v>
       </c>
       <c r="O41" t="n">
-        <v>4.22</v>
+        <v>2.79</v>
       </c>
       <c r="P41" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.1</v>
+        <v>4.32</v>
       </c>
       <c r="R41" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="T41" t="n">
-        <v>3.52</v>
+        <v>3.28</v>
       </c>
       <c r="U41" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V41" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="X41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>2.37</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.9</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45925.65625</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.82</v>
+        <v>2.53</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="O42" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S42" t="n">
         <v>2.4</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,43 +5958,43 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>6.6</v>
+        <v>1.82</v>
       </c>
       <c r="M43" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.46</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>2.2</v>
@@ -6003,16 +6003,16 @@
         <v>1.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>2.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45925.65625</v>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="M47" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O47" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.07</v>
+        <v>4.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S47" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T47" t="n">
         <v>3.5</v>
       </c>
       <c r="U47" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V47" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W47" t="n">
         <v>1.55</v>
       </c>
       <c r="X47" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AI47" t="n">
         <v>1.8</v>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
         <v>4.2</v>
@@ -7131,7 +7131,7 @@
         <v>2.55</v>
       </c>
       <c r="P52" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q52" t="n">
         <v>4.91</v>
@@ -7143,7 +7143,7 @@
         <v>2.56</v>
       </c>
       <c r="T52" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U52" t="n">
         <v>1.3</v>
@@ -7158,22 +7158,22 @@
         <v>2.71</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC52" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AI52" t="n">
         <v>1.66</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="M53" t="n">
-        <v>2.87</v>
+        <v>3.21</v>
       </c>
       <c r="N53" t="n">
-        <v>3.23</v>
+        <v>3.48</v>
       </c>
       <c r="O53" t="n">
         <v>2.88</v>
@@ -7266,7 +7266,7 @@
         <v>3.9</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S53" t="n">
         <v>2.56</v>
@@ -7278,28 +7278,28 @@
         <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X53" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AB53" t="n">
         <v>1.16</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD53" t="n">
         <v>1.83</v>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AI53" t="n">
         <v>1.83</v>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK53"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,94 +781,94 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="M3" t="n">
-        <v>3.69</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
         <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>5.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
         <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '61', '64', '75', '86']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AI3" t="n">
         <v>1.83</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
         <v>3.25</v>
@@ -1095,10 +1095,10 @@
         <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,39 +1159,39 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Al-Rustaq</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Bahla</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dhofar</t>
-        </is>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45925.43402777778</v>
+        <v>45925.43055555555</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.45</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
         <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1506,23 +1506,23 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45925.4375</v>
+        <v>45925.43402777778</v>
       </c>
     </row>
     <row r="9">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1581,34 +1581,34 @@
         <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Y9" t="n">
         <v>2.35</v>
@@ -1617,16 +1617,16 @@
         <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" t="n">
         <v>1.4</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,112 +1675,112 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.09</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
-        <v>9.34</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.38</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>14</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.95</v>
+        <v>2.72</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>5.74</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.83</v>
+        <v>1.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>3.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '86']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.15</v>
+        <v>1.79</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45925.45833333334</v>
+        <v>45925.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.83</v>
+        <v>1.09</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>9.34</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>20</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.77</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>2.89</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>3.47</v>
+        <v>5.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>6.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.38</v>
+        <v>1.16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.77</v>
+        <v>4.75</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45925.47916666666</v>
+        <v>45925.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45925.5</v>
+        <v>45925.47916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,91 +2062,91 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '45+3']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45925.5</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.16</v>
+        <v>3.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>3.28</v>
+        <v>5.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.04</v>
+        <v>2.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45925.50694444445</v>
+        <v>45925.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,86 +2346,86 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="P15" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.47</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AI15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AK15" s="3" t="n">
-        <v>45925.51041666666</v>
+        <v>45925.50694444445</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.76</v>
+        <v>6.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
         <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.58</v>
+        <v>2.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45925.51736111111</v>
+        <v>45925.51041666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,86 +2604,86 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.7</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.53</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45925.52083333334</v>
+        <v>45925.51736111111</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.57</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="O18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.05</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45925.53125</v>
+        <v>45925.52083333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2935,13 +2935,13 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45925.53472222222</v>
+        <v>45925.53125</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45925.54166666666</v>
+        <v>45925.53472222222</v>
       </c>
     </row>
     <row r="21">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,86 +3249,86 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N22" t="n">
         <v>2.4</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.75</v>
-      </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.13</v>
+        <v>2.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="U22" t="n">
         <v>1.41</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AK22" s="3" t="n">
-        <v>45925.55208333334</v>
+        <v>45925.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.61</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.94</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,16 +3448,16 @@
         <v>1.25</v>
       </c>
       <c r="AH23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.95</v>
       </c>
-      <c r="AI23" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45925.5625</v>
+        <v>45925.55208333334</v>
       </c>
     </row>
     <row r="24">
@@ -3516,13 +3516,13 @@
         <v>3.47</v>
       </c>
       <c r="O24" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="P24" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.26</v>
+        <v>4.13</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
@@ -3534,7 +3534,7 @@
         <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
@@ -3555,13 +3555,13 @@
         <v>3.68</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.84</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.34</v>
+        <v>7.1</v>
       </c>
       <c r="O25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.65</v>
       </c>
-      <c r="P25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.43</v>
-      </c>
       <c r="T25" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="U25" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.53</v>
+        <v>2.02</v>
       </c>
       <c r="M26" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>3.64</v>
       </c>
       <c r="O26" t="n">
-        <v>3.51</v>
+        <v>2.82</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S26" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="T26" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="M27" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N27" t="n">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="O27" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="T27" t="n">
         <v>3.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X27" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
         <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45925.5625</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,43 +4023,43 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>7.1</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.45</v>
+        <v>4.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
         <v>2.94</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.97</v>
       </c>
       <c r="Y28" t="n">
         <v>1.9</v>
@@ -4068,16 +4068,16 @@
         <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45925.5625</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="O29" t="n">
-        <v>3.94</v>
+        <v>3.51</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>5.08</v>
+        <v>2.65</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.33</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,19 +4219,19 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45925.58333333334</v>
+        <v>45925.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="O30" t="n">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.5</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>3.28</v>
+        <v>4.74</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,31 +4410,31 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="N31" t="n">
-        <v>4.05</v>
+        <v>1.52</v>
       </c>
       <c r="O31" t="n">
-        <v>2.36</v>
+        <v>7.02</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.33</v>
+        <v>1.87</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="U31" t="n">
         <v>1.54</v>
@@ -4443,28 +4443,28 @@
         <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X31" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.03</v>
+        <v>1.08</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="M32" t="n">
-        <v>4.47</v>
+        <v>3.66</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="T32" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.88</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.23</v>
+        <v>2.85</v>
       </c>
       <c r="P34" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.04</v>
+        <v>3.86</v>
       </c>
       <c r="T34" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="U34" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X34" t="n">
-        <v>3.58</v>
+        <v>5.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.04</v>
+        <v>1.46</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45925.58333333334</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,28 +4926,28 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="N35" t="n">
         <v>6</v>
       </c>
-      <c r="M35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.4</v>
-      </c>
       <c r="O35" t="n">
-        <v>5.95</v>
+        <v>2.01</v>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.88</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T35" t="n">
         <v>2.34</v>
@@ -4956,31 +4956,31 @@
         <v>1.56</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>4.86</v>
+        <v>4.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AC35" t="n">
         <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>2.75</v>
+        <v>1.1</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.44</v>
+        <v>2.87</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45925.58333333334</v>
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="M36" t="n">
-        <v>3.11</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="O36" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>3.41</v>
+        <v>2.28</v>
       </c>
       <c r="U36" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="V36" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.44</v>
+        <v>1.58</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,19 +5122,19 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45925.60416666666</v>
+        <v>45925.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>8</v>
+        <v>2.02</v>
       </c>
       <c r="M37" t="n">
-        <v>4.33</v>
+        <v>3.11</v>
       </c>
       <c r="N37" t="n">
-        <v>1.38</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>7</v>
+        <v>2.71</v>
       </c>
       <c r="P37" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>5.05</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.58</v>
+        <v>3.41</v>
       </c>
       <c r="U37" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="X37" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AC37" t="n">
         <v>2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.87</v>
+        <v>1.76</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45925.60416666666</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.07</v>
+        <v>6.2</v>
       </c>
       <c r="M38" t="n">
-        <v>7.75</v>
+        <v>4.5</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>1.38</v>
       </c>
       <c r="O38" t="n">
+        <v>7</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.43</v>
       </c>
-      <c r="P38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.73</v>
-      </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X38" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,19 +5380,19 @@
         </is>
       </c>
       <c r="AG38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.03</v>
       </c>
-      <c r="AH38" t="n">
-        <v>9</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1.11</v>
+        <v>2.87</v>
       </c>
       <c r="AJ38" t="n">
-        <v>5.75</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45925.625</v>
+        <v>45925.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>1.09</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>7.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
-        <v>2.86</v>
+        <v>1.43</v>
       </c>
       <c r="P39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.12</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.57</v>
+        <v>2.61</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.23</v>
+        <v>1.48</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.55</v>
+        <v>4.95</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.05</v>
+        <v>5.75</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45925.625</v>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.6</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>1.46</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>2.84</v>
       </c>
       <c r="P40" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z40" t="n">
         <v>2.1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AA40" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,19 +5638,19 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.1</v>
+        <v>1.81</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45925.65625</v>
+        <v>45925.625</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O41" t="n">
+        <v>6</v>
+      </c>
+      <c r="P41" t="n">
         <v>2.02</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q41" t="n">
-        <v>4.32</v>
+        <v>2.1</v>
       </c>
       <c r="R41" t="n">
         <v>1.47</v>
       </c>
       <c r="S41" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="T41" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.61</v>
+        <v>1.06</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45925.65625</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.53</v>
+        <v>1.82</v>
       </c>
       <c r="M42" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
-        <v>4.22</v>
+        <v>2.4</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45925.65625</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.82</v>
+        <v>2.53</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>2.78</v>
       </c>
       <c r="O43" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S43" t="n">
         <v>2.4</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45925.65625</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.09</v>
+        <v>2.02</v>
       </c>
       <c r="M44" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.12</v>
+        <v>3.56</v>
       </c>
       <c r="O44" t="n">
-        <v>3.02</v>
+        <v>2.71</v>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.77</v>
+        <v>4.38</v>
       </c>
       <c r="R44" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="S44" t="n">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="T44" t="n">
-        <v>2.19</v>
+        <v>3.22</v>
       </c>
       <c r="U44" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>2.55</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.73</v>
+        <v>1.62</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,16 +6157,16 @@
         <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45925.66666666666</v>
+        <v>45925.65625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>11</v>
+        <v>3.09</v>
       </c>
       <c r="M45" t="n">
-        <v>6.75</v>
+        <v>3.09</v>
       </c>
       <c r="N45" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="O45" t="n">
-        <v>7.5</v>
+        <v>3.02</v>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.67</v>
+        <v>2.77</v>
       </c>
       <c r="R45" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S45" t="n">
-        <v>4.15</v>
+        <v>3.56</v>
       </c>
       <c r="T45" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="U45" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W45" t="n">
         <v>1.11</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,19 +6283,19 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.5</v>
+        <v>1.76</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.28</v>
+        <v>2.01</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45925.6875</v>
+        <v>45925.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.66</v>
+        <v>11</v>
       </c>
       <c r="M46" t="n">
-        <v>3.29</v>
+        <v>6.75</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>1.22</v>
       </c>
       <c r="O46" t="n">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
       <c r="P46" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.72</v>
+        <v>1.67</v>
       </c>
       <c r="R46" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="S46" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="T46" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="U46" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>3.96</v>
+        <v>6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.08</v>
       </c>
-      <c r="AA46" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,19 +6412,19 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.95</v>
+        <v>1.05</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45925.77083333334</v>
+        <v>45925.6875</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.29</v>
       </c>
       <c r="N47" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="P47" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="R47" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="S47" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="U47" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="X47" t="n">
-        <v>2.45</v>
+        <v>3.96</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.61</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.46</v>
+        <v>2.08</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.9</v>
+        <v>2.49</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45925.79166666666</v>
+        <v>45925.77083333334</v>
       </c>
     </row>
     <row r="48">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>5.05</v>
+        <v>4.3</v>
       </c>
       <c r="O49" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q49" t="n">
         <v>4.75</v>
       </c>
       <c r="R49" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="S49" t="n">
-        <v>2.84</v>
+        <v>2.34</v>
       </c>
       <c r="T49" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="U49" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W49" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="X49" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.41</v>
+        <v>1.52</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.24</v>
+        <v>4.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.65</v>
+        <v>2.21</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,19 +6799,19 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45925.85416666666</v>
+        <v>45925.79166666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="M50" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="N50" t="n">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="O50" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="P50" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.07</v>
+        <v>4.75</v>
       </c>
       <c r="R50" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S50" t="n">
-        <v>3.56</v>
+        <v>2.84</v>
       </c>
       <c r="T50" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="U50" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
       </c>
       <c r="W50" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X50" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,19 +6928,19 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45925.875</v>
+        <v>45925.85416666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,86 +6990,86 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.33</v>
+        <v>1.56</v>
       </c>
       <c r="M51" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>4.7</v>
       </c>
       <c r="O51" t="n">
-        <v>4.35</v>
+        <v>1.99</v>
       </c>
       <c r="P51" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.92</v>
+        <v>5.07</v>
       </c>
       <c r="R51" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>2.51</v>
+        <v>3.56</v>
       </c>
       <c r="T51" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="U51" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="X51" t="n">
-        <v>2.56</v>
+        <v>4.85</v>
       </c>
       <c r="Y51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH51" t="n">
         <v>2.35</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AI51" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45925.89583333334</v>
+        <v>45925.875</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,58 +7119,58 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>3.33</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>4.35</v>
       </c>
       <c r="P52" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.91</v>
+        <v>2.92</v>
       </c>
       <c r="R52" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="T52" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U52" t="n">
         <v>1.3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X52" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AA52" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD52" t="n">
         <v>1.72</v>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45925.89583333334</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,85 +7248,214 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="M53" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="N53" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.9</v>
+        <v>4.91</v>
       </c>
       <c r="R53" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S53" t="n">
         <v>2.56</v>
       </c>
       <c r="T53" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U53" t="n">
         <v>1.3</v>
       </c>
       <c r="V53" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45925.89583333334</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V54" t="n">
         <v>1.08</v>
       </c>
-      <c r="W53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA53" t="n">
+      <c r="W54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA54" t="n">
         <v>4.15</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AB54" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AC54" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AD54" t="n">
         <v>1.83</v>
       </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH54" t="n">
         <v>1.63</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AI54" t="n">
         <v>1.83</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AJ54" t="n">
         <v>2.3</v>
       </c>
-      <c r="AK53" s="3" t="n">
+      <c r="AK54" s="3" t="n">
         <v>45925.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-09-25.xlsx
+++ b/jogos_2025-09-25.xlsx
@@ -1159,39 +1159,39 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1288,39 +1288,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Al-Rustaq</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Bahla</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dhofar</t>
-        </is>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1942,20 +1942,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '69']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.73</v>
+        <v>4.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>2.79</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['20', '45+3']</t>
+          <t>['42', '83']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '44', '90+1']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45925.5</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.05</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.57</v>
-      </c>
       <c r="Q14" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['20', '45+3']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45925.5</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2458,94 +2458,94 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.57</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
         <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '79']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AI16" t="n">
         <v>1.18</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '90']</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3116,87 +3116,87 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.7</v>
+        <v>2.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.93</v>
+        <v>3.17</v>
       </c>
       <c r="N21" t="n">
-        <v>1.58</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>4.29</v>
+        <v>3.67</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.21</v>
+        <v>2.91</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AA21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI21" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.61</v>
+        <v>4.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.34</v>
+        <v>3.93</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>4.29</v>
       </c>
       <c r="P22" t="n">
-        <v>2.11</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.76</v>
+        <v>2.21</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.93</v>
       </c>
-      <c r="AA22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45925.54166666666</v>
@@ -3361,20 +3361,20 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59', '67']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG23" t="n">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.03</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q24" t="n">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '45+1', '90+4']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45925.5625</v>
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>2.13</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.13</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.42</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X25" t="n">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '86']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45925.5625</v>
@@ -3739,87 +3739,87 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>3.64</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.82</v>
+        <v>3.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3828,20 +3828,20 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '38', '44']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45925.5625</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
         <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45925.5625</v>
@@ -3997,87 +3997,87 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="P28" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.4</v>
+        <v>6.56</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4086,20 +4086,20 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45925.5625</v>
@@ -4126,57 +4126,57 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="N29" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>3.51</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
         <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="T29" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
         <v>1.28</v>
@@ -4185,50 +4185,50 @@
         <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X29" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '54', '72']</t>
         </is>
       </c>
       <c r="AG29" t="n">
         <v>1.36</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.99</v>
+        <v>2.49</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45925.5625</v>
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.6</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>1.82</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.98</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.41</v>
+        <v>3.11</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="X30" t="n">
-        <v>4.74</v>
+        <v>3.36</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr"